--- a/tools/comparison_outputs/Alta_Lisboa_radiation_comparison.xlsx
+++ b/tools/comparison_outputs/Alta_Lisboa_radiation_comparison.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98,7 +98,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -155,7 +155,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -165,57 +165,97 @@
         </is>
       </c>
       <c r="B12">
-        <v>32049.17332839894</v>
+        <v>30354.990010648766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>total_ucea_roofs_top_m2_matched</t>
+          <t>total_validation_area_identified_by_oven_m2</t>
         </is>
       </c>
       <c r="B13">
-        <v>33369.13000000001</v>
+        <v>9439.73050004523</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>total_workflow0_roofs_top_m2_matched</t>
+          <t>oven_coverage_area_percentage</t>
         </is>
       </c>
       <c r="B14">
-        <v>31924.67999999999</v>
+        <v>31.09778819473734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>total_validation_radiation_kwh_year</t>
+          <t>total_ucea_roofs_top_m2_matched</t>
         </is>
       </c>
       <c r="B15">
-        <v>69071642.18416408</v>
+        <v>30364.06000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>total_ucea_radiation_kwh_year_matched</t>
+          <t>total_workflow0_roofs_top_m2_matched</t>
         </is>
       </c>
       <c r="B16">
-        <v>52289086.27999993</v>
+        <v>30231.489999999994</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>total_validation_radiation_kwh_year</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>69532427.88053128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>total_ucea_radiation_kwh_year_matched</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>50947617.550000004</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>total_workflow0_radiation_kwh_year_matched</t>
         </is>
       </c>
-      <c r="B17">
-        <v>50157797.44000004</v>
+      <c r="B19">
+        <v>50909874.920000024</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>oven_identified_error_percentage</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>-26.728263196077652</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>overall_error_percentage</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>-26.782543811828376</v>
       </c>
     </row>
   </sheetData>
@@ -224,7 +264,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -367,7 +407,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B1001</t>
+          <t>B1003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -376,28 +416,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>1694.1833177501749</v>
+        <v>316.63596337502787</v>
       </c>
       <c r="E2">
-        <v>1693.19</v>
+        <v>319.51</v>
       </c>
       <c r="F2">
-        <v>1693.19</v>
+        <v>316.6</v>
       </c>
       <c r="G2">
-        <v>3626073.48915625</v>
+        <v>722452.69621875</v>
       </c>
       <c r="H2">
-        <v>2738971.8100000024</v>
+        <v>539961.5199999999</v>
       </c>
       <c r="I2">
-        <v>2738180.9900000053</v>
+        <v>514414.79999999935</v>
       </c>
       <c r="J2">
-        <v>-887892.4991562446</v>
+        <v>-0.2879605783293516</v>
       </c>
       <c r="K2">
-        <v>-887101.6791562475</v>
+        <v>-0.2525994811478895</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -408,7 +448,7 @@
         <v>8760</v>
       </c>
       <c r="N2">
-        <v>2794.0</v>
+        <v>522.0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -437,6 +477,21 @@
       </c>
       <c r="U2">
         <v>8760</v>
+      </c>
+      <c r="V2">
+        <v>3.0</v>
+      </c>
+      <c r="W2">
+        <v>0.6940101385116577</v>
+      </c>
+      <c r="X2">
+        <v>0.634689014100703</v>
+      </c>
+      <c r="Y2">
+        <v>0.4489450454711914</v>
+      </c>
+      <c r="Z2">
+        <v>0.9342138767242432</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +502,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B1003</t>
+          <t>B1005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -456,28 +511,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>316.63596337502787</v>
+        <v>3044.282509224441</v>
       </c>
       <c r="E3">
-        <v>319.93</v>
+        <v>3044.94</v>
       </c>
       <c r="F3">
-        <v>316.6</v>
+        <v>3044.94</v>
       </c>
       <c r="G3">
-        <v>673715.56003125</v>
+        <v>6461016.0353125</v>
       </c>
       <c r="H3">
-        <v>504094.1399999998</v>
+        <v>5279354.109999982</v>
       </c>
       <c r="I3">
-        <v>479241.2899999988</v>
+        <v>5279952.880000014</v>
       </c>
       <c r="J3">
-        <v>-194474.2700312512</v>
+        <v>-0.1827983631146276</v>
       </c>
       <c r="K3">
-        <v>-169621.42003125022</v>
+        <v>-0.1828910373932178</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -488,7 +543,7 @@
         <v>8760</v>
       </c>
       <c r="N3">
-        <v>522.0</v>
+        <v>5021.0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -517,21 +572,6 @@
       </c>
       <c r="U3">
         <v>8760</v>
-      </c>
-      <c r="V3">
-        <v>3.0</v>
-      </c>
-      <c r="W3">
-        <v>0.6940101385116577</v>
-      </c>
-      <c r="X3">
-        <v>0.6345650829909568</v>
-      </c>
-      <c r="Y3">
-        <v>0.4489450454711914</v>
-      </c>
-      <c r="Z3">
-        <v>0.9342138767242432</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +582,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B1005</t>
+          <t>B1006</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -551,28 +591,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>3044.282509224441</v>
+        <v>1104.2171986477667</v>
       </c>
       <c r="E4">
-        <v>3044.94</v>
+        <v>1069.06</v>
       </c>
       <c r="F4">
-        <v>3044.94</v>
+        <v>1069.06</v>
       </c>
       <c r="G4">
-        <v>6229377.702179688</v>
+        <v>2151885.359375</v>
       </c>
       <c r="H4">
-        <v>4924717.719999996</v>
+        <v>1633554.3200000057</v>
       </c>
       <c r="I4">
-        <v>4924874.900000008</v>
+        <v>1633098.3799999994</v>
       </c>
       <c r="J4">
-        <v>-1304502.8021796802</v>
+        <v>-0.24108485943028052</v>
       </c>
       <c r="K4">
-        <v>-1304659.982179692</v>
+        <v>-0.24087298011337369</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -583,7 +623,7 @@
         <v>8760</v>
       </c>
       <c r="N4">
-        <v>5014.0</v>
+        <v>1818.0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -622,7 +662,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B1006</t>
+          <t>B1015</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -631,28 +671,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>1104.2171986477667</v>
+        <v>183.52575815737313</v>
       </c>
       <c r="E5">
-        <v>1069.06</v>
+        <v>180.52</v>
       </c>
       <c r="F5">
-        <v>1069.06</v>
+        <v>185.7</v>
       </c>
       <c r="G5">
-        <v>1851864.0273203126</v>
+        <v>382455.332625</v>
       </c>
       <c r="H5">
-        <v>1538797.5799999991</v>
+        <v>307023.2399999995</v>
       </c>
       <c r="I5">
-        <v>1540207.670000006</v>
+        <v>320436.45</v>
       </c>
       <c r="J5">
-        <v>-311656.3573203066</v>
+        <v>-0.1621598062166645</v>
       </c>
       <c r="K5">
-        <v>-313066.4473203134</v>
+        <v>-0.19723111744126764</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -663,7 +703,7 @@
         <v>8760</v>
       </c>
       <c r="N5">
-        <v>1821.0</v>
+        <v>301.0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -672,7 +712,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MULTI_RES</t>
+          <t>SINGLE_RES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -692,6 +732,21 @@
       </c>
       <c r="U5">
         <v>8760</v>
+      </c>
+      <c r="V5">
+        <v>2.0</v>
+      </c>
+      <c r="W5">
+        <v>0.6830049157142639</v>
+      </c>
+      <c r="X5">
+        <v>0.6836608447089686</v>
+      </c>
+      <c r="Y5">
+        <v>0.6775040626525879</v>
+      </c>
+      <c r="Z5">
+        <v>0.6885057687759399</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +757,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B1015</t>
+          <t>B1016</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,28 +766,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>183.52575815737313</v>
+        <v>515.4783622463749</v>
       </c>
       <c r="E6">
-        <v>311.82</v>
+        <v>515.67</v>
       </c>
       <c r="F6">
-        <v>185.7</v>
+        <v>515.67</v>
       </c>
       <c r="G6">
-        <v>351168.4384375</v>
+        <v>1041488.901328125</v>
       </c>
       <c r="H6">
-        <v>492921.50000000023</v>
+        <v>880636.9800000046</v>
       </c>
       <c r="I6">
-        <v>298758.6099999993</v>
+        <v>880725.7300000016</v>
       </c>
       <c r="J6">
-        <v>-52409.82843750069</v>
+        <v>-0.1543589865654021</v>
       </c>
       <c r="K6">
-        <v>141753.06156250025</v>
+        <v>-0.15444420110766344</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +798,7 @@
         <v>8760</v>
       </c>
       <c r="N6">
-        <v>305.0</v>
+        <v>850.0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -772,21 +827,6 @@
       </c>
       <c r="U6">
         <v>8760</v>
-      </c>
-      <c r="V6">
-        <v>2.0</v>
-      </c>
-      <c r="W6">
-        <v>0.6830049157142639</v>
-      </c>
-      <c r="X6">
-        <v>0.6830120318793079</v>
-      </c>
-      <c r="Y6">
-        <v>0.6775040626525879</v>
-      </c>
-      <c r="Z6">
-        <v>0.6885057687759399</v>
       </c>
     </row>
     <row r="7">
@@ -797,7 +837,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B1016</t>
+          <t>B1017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,28 +846,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>515.4783622463749</v>
+        <v>170.520331279709</v>
       </c>
       <c r="E7">
-        <v>515.67</v>
+        <v>174.33</v>
       </c>
       <c r="F7">
-        <v>515.67</v>
+        <v>174.33</v>
       </c>
       <c r="G7">
-        <v>875034.74315625</v>
+        <v>365252.92209375004</v>
       </c>
       <c r="H7">
-        <v>817084.9100000005</v>
+        <v>295944.91999999963</v>
       </c>
       <c r="I7">
-        <v>818658.0000000024</v>
+        <v>295766.63999999897</v>
       </c>
       <c r="J7">
-        <v>-56376.74315624754</v>
+        <v>-0.19024155014402847</v>
       </c>
       <c r="K7">
-        <v>-57949.833156249486</v>
+        <v>-0.18975345001062308</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -838,7 +878,7 @@
         <v>8760</v>
       </c>
       <c r="N7">
-        <v>848.0</v>
+        <v>282.0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -877,7 +917,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B1017</t>
+          <t>B1020</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -886,28 +926,28 @@
         </is>
       </c>
       <c r="D8">
-        <v>170.520331279709</v>
+        <v>4380.109525835609</v>
       </c>
       <c r="E8">
-        <v>174.33</v>
+        <v>4380.24</v>
       </c>
       <c r="F8">
-        <v>174.33</v>
+        <v>4380.24</v>
       </c>
       <c r="G8">
-        <v>311720.9159375</v>
+        <v>10438925.579078125</v>
       </c>
       <c r="H8">
-        <v>274540.7299999995</v>
+        <v>7525957.809999977</v>
       </c>
       <c r="I8">
-        <v>274598.4500000006</v>
+        <v>7524601.990000011</v>
       </c>
       <c r="J8">
-        <v>-37122.46593749942</v>
+        <v>-0.2791785004118672</v>
       </c>
       <c r="K8">
-        <v>-37180.1859375005</v>
+        <v>-0.2790486192292019</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -918,7 +958,7 @@
         <v>8760</v>
       </c>
       <c r="N8">
-        <v>280.0</v>
+        <v>7217.0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -927,7 +967,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SINGLE_RES</t>
+          <t>MULTI_RES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -957,7 +997,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B1020</t>
+          <t>B1022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -966,28 +1006,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>4380.109525835609</v>
+        <v>417.3871285856169</v>
       </c>
       <c r="E9">
-        <v>4380.24</v>
+        <v>417.39</v>
       </c>
       <c r="F9">
-        <v>4380.24</v>
+        <v>417.39</v>
       </c>
       <c r="G9">
-        <v>10414303.75825</v>
+        <v>1014674.485625</v>
       </c>
       <c r="H9">
-        <v>7006832.899999968</v>
+        <v>689365.6999999996</v>
       </c>
       <c r="I9">
-        <v>7005690.230000005</v>
+        <v>688799.9100000015</v>
       </c>
       <c r="J9">
-        <v>-3408613.528249995</v>
+        <v>-0.3211616929780908</v>
       </c>
       <c r="K9">
-        <v>-3407470.858250032</v>
+        <v>-0.3206040855798427</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -998,7 +1038,7 @@
         <v>8760</v>
       </c>
       <c r="N9">
-        <v>7223.0</v>
+        <v>687.0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1037,7 +1077,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B1022</t>
+          <t>B1026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1046,28 +1086,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>417.3871285856169</v>
+        <v>1667.5706794638463</v>
       </c>
       <c r="E10">
-        <v>417.39</v>
+        <v>1610.04</v>
       </c>
       <c r="F10">
-        <v>417.39</v>
+        <v>1610.04</v>
       </c>
       <c r="G10">
-        <v>1019369.598</v>
+        <v>3759624.0890078126</v>
       </c>
       <c r="H10">
-        <v>634126.8899999986</v>
+        <v>2789762.56999999</v>
       </c>
       <c r="I10">
-        <v>633718.5399999999</v>
+        <v>2789624.430000003</v>
       </c>
       <c r="J10">
-        <v>-385651.0580000001</v>
+        <v>-0.2580044270499922</v>
       </c>
       <c r="K10">
-        <v>-385242.7080000014</v>
+        <v>-0.2579676840148598</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1078,7 +1118,7 @@
         <v>8760</v>
       </c>
       <c r="N10">
-        <v>683.0</v>
+        <v>2750.0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1117,7 +1157,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B1026</t>
+          <t>B1031</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1126,28 +1166,28 @@
         </is>
       </c>
       <c r="D11">
-        <v>1667.5706794638463</v>
+        <v>741.4124896180284</v>
       </c>
       <c r="E11">
-        <v>1610.04</v>
+        <v>741.41</v>
       </c>
       <c r="F11">
-        <v>1610.04</v>
+        <v>741.41</v>
       </c>
       <c r="G11">
-        <v>3340821.5243984377</v>
+        <v>1449804.290203125</v>
       </c>
       <c r="H11">
-        <v>2601219.4200000083</v>
+        <v>1287157.4100000015</v>
       </c>
       <c r="I11">
-        <v>2599879.419999997</v>
+        <v>1287503.8899999992</v>
       </c>
       <c r="J11">
-        <v>-740942.1043984406</v>
+        <v>-0.11194642014777503</v>
       </c>
       <c r="K11">
-        <v>-739602.1043984294</v>
+        <v>-0.11218540412812254</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1158,7 +1198,7 @@
         <v>8760</v>
       </c>
       <c r="N11">
-        <v>2757.0</v>
+        <v>1215.0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1197,7 +1237,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B1031</t>
+          <t>B1033</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1206,28 +1246,28 @@
         </is>
       </c>
       <c r="D12">
-        <v>741.4124896180284</v>
+        <v>378.38995699688985</v>
       </c>
       <c r="E12">
-        <v>741.41</v>
+        <v>378.38</v>
       </c>
       <c r="F12">
-        <v>741.41</v>
+        <v>378.38</v>
       </c>
       <c r="G12">
-        <v>1228701.8498984375</v>
+        <v>951905.74384375</v>
       </c>
       <c r="H12">
-        <v>1199817.0000000014</v>
+        <v>625601.8699999992</v>
       </c>
       <c r="I12">
-        <v>1200865.0400000012</v>
+        <v>627903.4000000013</v>
       </c>
       <c r="J12">
-        <v>-27836.809898436302</v>
+        <v>-0.34037229624799054</v>
       </c>
       <c r="K12">
-        <v>-28884.849898436107</v>
+        <v>-0.3427901091615976</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1238,7 +1278,7 @@
         <v>8760</v>
       </c>
       <c r="N12">
-        <v>1230.0</v>
+        <v>622.0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1267,6 +1307,21 @@
       </c>
       <c r="U12">
         <v>8760</v>
+      </c>
+      <c r="V12">
+        <v>1.0</v>
+      </c>
+      <c r="W12">
+        <v>0.9890090823173523</v>
+      </c>
+      <c r="X12">
+        <v>0.9890090823173523</v>
+      </c>
+      <c r="Y12">
+        <v>0.9890090823173523</v>
+      </c>
+      <c r="Z12">
+        <v>0.9890090823173523</v>
       </c>
     </row>
     <row r="13">
@@ -1277,7 +1332,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B1033</t>
+          <t>B1034</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1286,28 +1341,28 @@
         </is>
       </c>
       <c r="D13">
-        <v>378.38995699688985</v>
+        <v>694.9341439901845</v>
       </c>
       <c r="E13">
-        <v>380.28</v>
+        <v>677.84</v>
       </c>
       <c r="F13">
-        <v>378.38</v>
+        <v>677.84</v>
       </c>
       <c r="G13">
-        <v>880467.477890625</v>
+        <v>1432575.848921875</v>
       </c>
       <c r="H13">
-        <v>585019.369999999</v>
+        <v>1078085.9100000006</v>
       </c>
       <c r="I13">
-        <v>586851.9600000022</v>
+        <v>1078304.2700000012</v>
       </c>
       <c r="J13">
-        <v>-293615.51789062284</v>
+        <v>-0.24729690870364093</v>
       </c>
       <c r="K13">
-        <v>-295448.10789062607</v>
+        <v>-0.24744933344273234</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1318,7 +1373,7 @@
         <v>8760</v>
       </c>
       <c r="N13">
-        <v>623.0</v>
+        <v>1148.0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1347,21 +1402,6 @@
       </c>
       <c r="U13">
         <v>8760</v>
-      </c>
-      <c r="V13">
-        <v>1.0</v>
-      </c>
-      <c r="W13">
-        <v>0.9890090823173523</v>
-      </c>
-      <c r="X13">
-        <v>0.9890090823173523</v>
-      </c>
-      <c r="Y13">
-        <v>0.9890090823173523</v>
-      </c>
-      <c r="Z13">
-        <v>0.9890090823173523</v>
       </c>
     </row>
     <row r="14">
@@ -1372,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B1034</t>
+          <t>B1035</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1381,28 +1421,28 @@
         </is>
       </c>
       <c r="D14">
-        <v>694.9341439901845</v>
+        <v>735.2452728248661</v>
       </c>
       <c r="E14">
-        <v>677.84</v>
+        <v>734.71</v>
       </c>
       <c r="F14">
-        <v>677.84</v>
+        <v>732.46</v>
       </c>
       <c r="G14">
-        <v>1415326.329546875</v>
+        <v>1445044.5366953125</v>
       </c>
       <c r="H14">
-        <v>1014222.9800000013</v>
+        <v>1272632.4800000037</v>
       </c>
       <c r="I14">
-        <v>1014387.1100000015</v>
+        <v>1270517.9199999978</v>
       </c>
       <c r="J14">
-        <v>-400939.2195468736</v>
+        <v>-0.1207759430684686</v>
       </c>
       <c r="K14">
-        <v>-401103.3495468738</v>
+        <v>-0.11931262484795085</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1413,7 +1453,7 @@
         <v>8760</v>
       </c>
       <c r="N14">
-        <v>1148.0</v>
+        <v>1215.0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1442,6 +1482,21 @@
       </c>
       <c r="U14">
         <v>8760</v>
+      </c>
+      <c r="V14">
+        <v>1.0</v>
+      </c>
+      <c r="W14">
+        <v>0.9921562671661377</v>
+      </c>
+      <c r="X14">
+        <v>0.9921562671661377</v>
+      </c>
+      <c r="Y14">
+        <v>0.9921562671661377</v>
+      </c>
+      <c r="Z14">
+        <v>0.9921562671661377</v>
       </c>
     </row>
     <row r="15">
@@ -1452,7 +1507,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B1035</t>
+          <t>B1037</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1461,28 +1516,28 @@
         </is>
       </c>
       <c r="D15">
-        <v>735.2452728248661</v>
+        <v>483.60073633411224</v>
       </c>
       <c r="E15">
-        <v>1099.25</v>
+        <v>474.2</v>
       </c>
       <c r="F15">
-        <v>732.46</v>
+        <v>474.2</v>
       </c>
       <c r="G15">
-        <v>1410786.6916328126</v>
+        <v>1096379.78125</v>
       </c>
       <c r="H15">
-        <v>1779921.6899999976</v>
+        <v>743965.810000001</v>
       </c>
       <c r="I15">
-        <v>1184036.8100000005</v>
+        <v>746862.0799999982</v>
       </c>
       <c r="J15">
-        <v>-226749.8816328121</v>
+        <v>-0.3187925454549254</v>
       </c>
       <c r="K15">
-        <v>369134.998367185</v>
+        <v>-0.32143421219260926</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1493,7 +1548,7 @@
         <v>8760</v>
       </c>
       <c r="N15">
-        <v>1216.0</v>
+        <v>799.0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1522,21 +1577,6 @@
       </c>
       <c r="U15">
         <v>8760</v>
-      </c>
-      <c r="V15">
-        <v>1.0</v>
-      </c>
-      <c r="W15">
-        <v>0.9921562671661377</v>
-      </c>
-      <c r="X15">
-        <v>0.9921562671661377</v>
-      </c>
-      <c r="Y15">
-        <v>0.9921562671661377</v>
-      </c>
-      <c r="Z15">
-        <v>0.9921562671661377</v>
       </c>
     </row>
     <row r="16">
@@ -1547,7 +1587,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B1037</t>
+          <t>B1038</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1556,28 +1596,28 @@
         </is>
       </c>
       <c r="D16">
-        <v>483.60073633411224</v>
+        <v>503.4881674734263</v>
       </c>
       <c r="E16">
-        <v>474.2</v>
+        <v>497.04</v>
       </c>
       <c r="F16">
-        <v>474.2</v>
+        <v>491.6</v>
       </c>
       <c r="G16">
-        <v>1141347.0878437501</v>
+        <v>1165644.1205625</v>
       </c>
       <c r="H16">
-        <v>701826.8100000017</v>
+        <v>862701.0899999981</v>
       </c>
       <c r="I16">
-        <v>708260.1400000021</v>
+        <v>853288.3800000006</v>
       </c>
       <c r="J16">
-        <v>-433086.947843748</v>
+        <v>-0.26796835762511056</v>
       </c>
       <c r="K16">
-        <v>-439520.27784374845</v>
+        <v>-0.2598932429018833</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1588,7 +1628,7 @@
         <v>8760</v>
       </c>
       <c r="N16">
-        <v>797.0</v>
+        <v>829.0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1617,6 +1657,21 @@
       </c>
       <c r="U16">
         <v>8760</v>
+      </c>
+      <c r="V16">
+        <v>1.0</v>
+      </c>
+      <c r="W16">
+        <v>0.9971573352813721</v>
+      </c>
+      <c r="X16">
+        <v>0.9971573352813721</v>
+      </c>
+      <c r="Y16">
+        <v>0.9971573352813721</v>
+      </c>
+      <c r="Z16">
+        <v>0.9971573352813721</v>
       </c>
     </row>
     <row r="17">
@@ -1627,7 +1682,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B1038</t>
+          <t>B1039</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1636,28 +1691,28 @@
         </is>
       </c>
       <c r="D17">
-        <v>503.4881674734263</v>
+        <v>554.508292101786</v>
       </c>
       <c r="E17">
-        <v>685.11</v>
+        <v>559.37</v>
       </c>
       <c r="F17">
-        <v>491.6</v>
+        <v>559.37</v>
       </c>
       <c r="G17">
-        <v>1057462.0822109375</v>
+        <v>1269227.792875</v>
       </c>
       <c r="H17">
-        <v>1108829.8399999947</v>
+        <v>971308.1000000042</v>
       </c>
       <c r="I17">
-        <v>795441.8999999954</v>
+        <v>970665.6400000021</v>
       </c>
       <c r="J17">
-        <v>-262020.18221094215</v>
+        <v>-0.2352313387329061</v>
       </c>
       <c r="K17">
-        <v>51367.757789057214</v>
+        <v>-0.23472515693984375</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1668,7 +1723,7 @@
         <v>8760</v>
       </c>
       <c r="N17">
-        <v>833.0</v>
+        <v>912.0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1697,21 +1752,6 @@
       </c>
       <c r="U17">
         <v>8760</v>
-      </c>
-      <c r="V17">
-        <v>1.0</v>
-      </c>
-      <c r="W17">
-        <v>0.9971573352813721</v>
-      </c>
-      <c r="X17">
-        <v>0.9971573352813721</v>
-      </c>
-      <c r="Y17">
-        <v>0.9971573352813721</v>
-      </c>
-      <c r="Z17">
-        <v>0.9971573352813721</v>
       </c>
     </row>
     <row r="18">
@@ -1722,7 +1762,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B1039</t>
+          <t>B1040</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1731,28 +1771,28 @@
         </is>
       </c>
       <c r="D18">
-        <v>554.508292101786</v>
+        <v>409.8525790272137</v>
       </c>
       <c r="E18">
-        <v>559.37</v>
+        <v>430.84</v>
       </c>
       <c r="F18">
-        <v>559.37</v>
+        <v>430.84</v>
       </c>
       <c r="G18">
-        <v>1140396.1570078125</v>
+        <v>934826.555390625</v>
       </c>
       <c r="H18">
-        <v>905124.9099999999</v>
+        <v>671672.1199999972</v>
       </c>
       <c r="I18">
-        <v>905111.9700000014</v>
+        <v>671548.7300000011</v>
       </c>
       <c r="J18">
-        <v>-235284.18700781115</v>
+        <v>-0.2816328054358822</v>
       </c>
       <c r="K18">
-        <v>-235271.2470078126</v>
+        <v>-0.2815008130365601</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1763,7 +1803,7 @@
         <v>8760</v>
       </c>
       <c r="N18">
-        <v>913.0</v>
+        <v>675.0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1802,7 +1842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B1040</t>
+          <t>B1041</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1811,28 +1851,28 @@
         </is>
       </c>
       <c r="D19">
-        <v>409.8525790272137</v>
+        <v>247.22561700996837</v>
       </c>
       <c r="E19">
-        <v>430.84</v>
+        <v>247.22</v>
       </c>
       <c r="F19">
-        <v>430.84</v>
+        <v>247.22</v>
       </c>
       <c r="G19">
-        <v>938017.342109375</v>
+        <v>516489.6829375</v>
       </c>
       <c r="H19">
-        <v>631905.6099999994</v>
+        <v>366093.43</v>
       </c>
       <c r="I19">
-        <v>631904.0900000011</v>
+        <v>365949.16999999905</v>
       </c>
       <c r="J19">
-        <v>-306113.2521093739</v>
+        <v>-0.291468577031998</v>
       </c>
       <c r="K19">
-        <v>-306111.73210937565</v>
+        <v>-0.2911892684518528</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1843,7 +1883,7 @@
         <v>8760</v>
       </c>
       <c r="N19">
-        <v>674.0</v>
+        <v>407.0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1882,7 +1922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B1041</t>
+          <t>B1042</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1891,28 +1931,28 @@
         </is>
       </c>
       <c r="D20">
-        <v>247.22561700996837</v>
+        <v>453.16461369242427</v>
       </c>
       <c r="E20">
-        <v>247.22</v>
+        <v>453.16</v>
       </c>
       <c r="F20">
-        <v>247.22</v>
+        <v>453.16</v>
       </c>
       <c r="G20">
-        <v>544955.57646875</v>
+        <v>1100404.8786875</v>
       </c>
       <c r="H20">
-        <v>351934.94000000093</v>
+        <v>784224.1900000022</v>
       </c>
       <c r="I20">
-        <v>352061.16000000027</v>
+        <v>784333.8800000036</v>
       </c>
       <c r="J20">
-        <v>-192894.41646874975</v>
+        <v>-0.28723154977692195</v>
       </c>
       <c r="K20">
-        <v>-193020.6364687491</v>
+        <v>-0.2873312312688218</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1923,7 +1963,7 @@
         <v>8760</v>
       </c>
       <c r="N20">
-        <v>409.0</v>
+        <v>748.0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1962,7 +2002,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B1042</t>
+          <t>B1043</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1971,28 +2011,28 @@
         </is>
       </c>
       <c r="D21">
-        <v>453.16461369242427</v>
+        <v>370.47287369398555</v>
       </c>
       <c r="E21">
-        <v>453.16</v>
+        <v>377.68</v>
       </c>
       <c r="F21">
-        <v>453.16</v>
+        <v>370.47</v>
       </c>
       <c r="G21">
-        <v>1113595.6709375</v>
+        <v>806421.4786093751</v>
       </c>
       <c r="H21">
-        <v>732594.5200000012</v>
+        <v>582757.56</v>
       </c>
       <c r="I21">
-        <v>732051.7999999998</v>
+        <v>586335.2300000011</v>
       </c>
       <c r="J21">
-        <v>-381543.87093750015</v>
+        <v>-0.27291714624082103</v>
       </c>
       <c r="K21">
-        <v>-381001.1509374988</v>
+        <v>-0.2773536228165325</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2003,7 +2043,7 @@
         <v>8760</v>
       </c>
       <c r="N21">
-        <v>751.0</v>
+        <v>608.0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2032,6 +2072,21 @@
       </c>
       <c r="U21">
         <v>8760</v>
+      </c>
+      <c r="V21">
+        <v>2.0</v>
+      </c>
+      <c r="W21">
+        <v>0.7904747724533081</v>
+      </c>
+      <c r="X21">
+        <v>0.801526068218561</v>
+      </c>
+      <c r="Y21">
+        <v>0.719028651714325</v>
+      </c>
+      <c r="Z21">
+        <v>0.8619208931922913</v>
       </c>
     </row>
     <row r="22">
@@ -2042,7 +2097,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B1043</t>
+          <t>B1044</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2051,28 +2106,28 @@
         </is>
       </c>
       <c r="D22">
-        <v>370.47287369398555</v>
+        <v>236.53398952913864</v>
       </c>
       <c r="E22">
-        <v>437.59</v>
+        <v>240.14</v>
       </c>
       <c r="F22">
-        <v>370.47</v>
+        <v>236.53</v>
       </c>
       <c r="G22">
-        <v>701489.609890625</v>
+        <v>559592.7028125001</v>
       </c>
       <c r="H22">
-        <v>632877.7600000008</v>
+        <v>367614.83000000066</v>
       </c>
       <c r="I22">
-        <v>536729.5199999992</v>
+        <v>366588.2300000012</v>
       </c>
       <c r="J22">
-        <v>-164760.0898906258</v>
+        <v>-0.34490169697078393</v>
       </c>
       <c r="K22">
-        <v>-68611.84989062417</v>
+        <v>-0.3430671483877882</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2083,7 +2138,7 @@
         <v>8760</v>
       </c>
       <c r="N22">
-        <v>613.0</v>
+        <v>391.0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2117,16 +2172,16 @@
         <v>2.0</v>
       </c>
       <c r="W22">
-        <v>0.7904747724533081</v>
+        <v>0.8522438108921051</v>
       </c>
       <c r="X22">
-        <v>0.7903868910624615</v>
+        <v>0.8521502356645682</v>
       </c>
       <c r="Y22">
-        <v>0.719028651714325</v>
+        <v>0.7339749336242676</v>
       </c>
       <c r="Z22">
-        <v>0.8619208931922913</v>
+        <v>0.9705126881599426</v>
       </c>
     </row>
     <row r="23">
@@ -2137,7 +2192,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B1044</t>
+          <t>B1045</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2146,28 +2201,28 @@
         </is>
       </c>
       <c r="D23">
-        <v>236.53398952913864</v>
+        <v>366.5435176578728</v>
       </c>
       <c r="E23">
-        <v>240.64</v>
+        <v>367.69</v>
       </c>
       <c r="F23">
-        <v>236.53</v>
+        <v>366.54</v>
       </c>
       <c r="G23">
-        <v>563281.8781875</v>
+        <v>890316.30021875</v>
       </c>
       <c r="H23">
-        <v>337315.3800000004</v>
+        <v>539951.5100000006</v>
       </c>
       <c r="I23">
-        <v>334985.99000000133</v>
+        <v>550439.9700000006</v>
       </c>
       <c r="J23">
-        <v>-228295.88818749873</v>
+        <v>-0.38174784639486226</v>
       </c>
       <c r="K23">
-        <v>-225966.49818749964</v>
+        <v>-0.3935284461630828</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2178,7 +2233,7 @@
         <v>8760</v>
       </c>
       <c r="N23">
-        <v>390.0</v>
+        <v>602.0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2209,19 +2264,19 @@
         <v>8760</v>
       </c>
       <c r="V23">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W23">
-        <v>0.8522438108921051</v>
+        <v>0.6310444076855978</v>
       </c>
       <c r="X23">
-        <v>0.852163693995782</v>
+        <v>0.6109359084130974</v>
       </c>
       <c r="Y23">
-        <v>0.7339749336242676</v>
+        <v>0.4843061566352844</v>
       </c>
       <c r="Z23">
-        <v>0.9705126881599426</v>
+        <v>0.9078754186630249</v>
       </c>
     </row>
     <row r="24">
@@ -2232,7 +2287,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B1045</t>
+          <t>B1046</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2241,28 +2296,28 @@
         </is>
       </c>
       <c r="D24">
-        <v>366.5435176578728</v>
+        <v>234.33676148704424</v>
       </c>
       <c r="E24">
-        <v>434.11</v>
+        <v>237.49</v>
       </c>
       <c r="F24">
-        <v>366.54</v>
+        <v>234.34</v>
       </c>
       <c r="G24">
-        <v>833995.7813515625</v>
+        <v>533411.51046875</v>
       </c>
       <c r="H24">
-        <v>581495.81</v>
+        <v>360033.9999999998</v>
       </c>
       <c r="I24">
-        <v>510463.68999999954</v>
+        <v>365907.7299999989</v>
       </c>
       <c r="J24">
-        <v>-323532.09135156294</v>
+        <v>-0.31402355813722993</v>
       </c>
       <c r="K24">
-        <v>-252499.97135156242</v>
+        <v>-0.3250351877791125</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2273,7 +2328,7 @@
         <v>8760</v>
       </c>
       <c r="N24">
-        <v>604.0</v>
+        <v>387.0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2304,19 +2359,19 @@
         <v>8760</v>
       </c>
       <c r="V24">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W24">
-        <v>0.6310444076855978</v>
+        <v>0.9972227513790131</v>
       </c>
       <c r="X24">
-        <v>0.5945103325432265</v>
+        <v>0.997224778035883</v>
       </c>
       <c r="Y24">
-        <v>0.4843061566352844</v>
+        <v>0.9952940344810486</v>
       </c>
       <c r="Z24">
-        <v>0.9078754186630249</v>
+        <v>0.9991514682769775</v>
       </c>
     </row>
     <row r="25">
@@ -2327,7 +2382,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B1046</t>
+          <t>B1047</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2336,28 +2391,28 @@
         </is>
       </c>
       <c r="D25">
-        <v>234.33676148704424</v>
+        <v>369.2005635828266</v>
       </c>
       <c r="E25">
-        <v>238.15</v>
+        <v>367.51</v>
       </c>
       <c r="F25">
-        <v>234.34</v>
+        <v>369.2</v>
       </c>
       <c r="G25">
-        <v>419237.2501796875</v>
+        <v>895263.256078125</v>
       </c>
       <c r="H25">
-        <v>336759.58999999973</v>
+        <v>543706.2000000003</v>
       </c>
       <c r="I25">
-        <v>341395.7900000004</v>
+        <v>582552.090000001</v>
       </c>
       <c r="J25">
-        <v>-77841.46017968713</v>
+        <v>-0.3492952089288419</v>
       </c>
       <c r="K25">
-        <v>-82477.66017968778</v>
+        <v>-0.3926856750696871</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2368,7 +2423,7 @@
         <v>8760</v>
       </c>
       <c r="N25">
-        <v>386.0</v>
+        <v>610.0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2399,19 +2454,19 @@
         <v>8760</v>
       </c>
       <c r="V25">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W25">
-        <v>0.9972227513790131</v>
+        <v>0.7484132647514343</v>
       </c>
       <c r="X25">
-        <v>0.997222278943757</v>
+        <v>0.6981701350214314</v>
       </c>
       <c r="Y25">
-        <v>0.9952940344810486</v>
+        <v>0.6164996027946472</v>
       </c>
       <c r="Z25">
-        <v>0.9991514682769775</v>
+        <v>0.938165545463562</v>
       </c>
     </row>
     <row r="26">
@@ -2422,7 +2477,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B1047</t>
+          <t>B1048</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2431,28 +2486,28 @@
         </is>
       </c>
       <c r="D26">
-        <v>369.2005635828266</v>
+        <v>239.06366887064294</v>
       </c>
       <c r="E26">
-        <v>434.06</v>
+        <v>244.91</v>
       </c>
       <c r="F26">
-        <v>369.2</v>
+        <v>239.06</v>
       </c>
       <c r="G26">
-        <v>838283.1327421875</v>
+        <v>588706.8608437501</v>
       </c>
       <c r="H26">
-        <v>614885.0999999982</v>
+        <v>395414.7900000012</v>
       </c>
       <c r="I26">
-        <v>547141.5600000006</v>
+        <v>393658.0000000021</v>
       </c>
       <c r="J26">
-        <v>-291141.57274218684</v>
+        <v>-0.331317458342848</v>
       </c>
       <c r="K26">
-        <v>-223398.03274218924</v>
+        <v>-0.3283333076273608</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2463,7 +2518,7 @@
         <v>8760</v>
       </c>
       <c r="N26">
-        <v>610.0</v>
+        <v>395.0</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2494,19 +2549,19 @@
         <v>8760</v>
       </c>
       <c r="V26">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W26">
-        <v>0.7484132647514343</v>
+        <v>0.9933198392391205</v>
       </c>
       <c r="X26">
-        <v>0.7340029237182558</v>
+        <v>0.9933143407200014</v>
       </c>
       <c r="Y26">
-        <v>0.6164996027946472</v>
+        <v>0.9876328706741333</v>
       </c>
       <c r="Z26">
-        <v>0.938165545463562</v>
+        <v>0.9990068078041077</v>
       </c>
     </row>
     <row r="27">
@@ -2517,7 +2572,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B1048</t>
+          <t>B1049</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2526,28 +2581,28 @@
         </is>
       </c>
       <c r="D27">
-        <v>239.06366887064294</v>
+        <v>371.1067151006221</v>
       </c>
       <c r="E27">
-        <v>245.35</v>
+        <v>374.3</v>
       </c>
       <c r="F27">
-        <v>239.06</v>
+        <v>371.11</v>
       </c>
       <c r="G27">
-        <v>585334.7185</v>
+        <v>850291.7773125</v>
       </c>
       <c r="H27">
-        <v>372831.0800000001</v>
+        <v>619176.9500000001</v>
       </c>
       <c r="I27">
-        <v>369790.1599999993</v>
+        <v>609268.8900000011</v>
       </c>
       <c r="J27">
-        <v>-215544.55850000068</v>
+        <v>-0.2834590357609892</v>
       </c>
       <c r="K27">
-        <v>-212503.63849999988</v>
+        <v>-0.27180649452236255</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2558,7 +2613,7 @@
         <v>8760</v>
       </c>
       <c r="N27">
-        <v>395.0</v>
+        <v>609.0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2592,16 +2647,16 @@
         <v>2.0</v>
       </c>
       <c r="W27">
-        <v>0.9933198392391205</v>
+        <v>0.813204437494278</v>
       </c>
       <c r="X27">
-        <v>0.9933133930918492</v>
+        <v>0.8330670060034264</v>
       </c>
       <c r="Y27">
-        <v>0.9876328706741333</v>
+        <v>0.6857811808586121</v>
       </c>
       <c r="Z27">
-        <v>0.9990068078041077</v>
+        <v>0.9406276941299438</v>
       </c>
     </row>
     <row r="28">
@@ -2612,7 +2667,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B1049</t>
+          <t>B1050</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2621,28 +2676,28 @@
         </is>
       </c>
       <c r="D28">
-        <v>371.1067151006221</v>
+        <v>370.7444376004047</v>
       </c>
       <c r="E28">
-        <v>433.19</v>
+        <v>371.19</v>
       </c>
       <c r="F28">
-        <v>371.11</v>
+        <v>370.74</v>
       </c>
       <c r="G28">
-        <v>735606.3704921876</v>
+        <v>893793.9065</v>
       </c>
       <c r="H28">
-        <v>683129.4699999983</v>
+        <v>593374.3999999996</v>
       </c>
       <c r="I28">
-        <v>565560.9399999987</v>
+        <v>594756.2800000008</v>
       </c>
       <c r="J28">
-        <v>-170045.4304921889</v>
+        <v>-0.3345711179336611</v>
       </c>
       <c r="K28">
-        <v>-52476.90049218922</v>
+        <v>-0.33611720142108675</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2653,7 +2708,7 @@
         <v>8760</v>
       </c>
       <c r="N28">
-        <v>614.0</v>
+        <v>612.0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2684,19 +2739,19 @@
         <v>8760</v>
       </c>
       <c r="V28">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W28">
-        <v>0.813204437494278</v>
+        <v>0.7062302728494009</v>
       </c>
       <c r="X28">
-        <v>0.8131838499631585</v>
+        <v>0.7655380594806622</v>
       </c>
       <c r="Y28">
-        <v>0.6857811808586121</v>
+        <v>0.4379631578922272</v>
       </c>
       <c r="Z28">
-        <v>0.9406276941299438</v>
+        <v>0.9300246238708496</v>
       </c>
     </row>
     <row r="29">
@@ -2707,7 +2762,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B1050</t>
+          <t>B1051</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2716,28 +2771,28 @@
         </is>
       </c>
       <c r="D29">
-        <v>370.7444376004047</v>
+        <v>237.23200376810422</v>
       </c>
       <c r="E29">
-        <v>437.5</v>
+        <v>242.52</v>
       </c>
       <c r="F29">
-        <v>370.74</v>
+        <v>237.23</v>
       </c>
       <c r="G29">
-        <v>841388.059640625</v>
+        <v>584574.7331875</v>
       </c>
       <c r="H29">
-        <v>628483.3200000002</v>
+        <v>406187.7499999999</v>
       </c>
       <c r="I29">
-        <v>542774.3700000006</v>
+        <v>356633.54000000097</v>
       </c>
       <c r="J29">
-        <v>-298613.68964062445</v>
+        <v>-0.38992652307192316</v>
       </c>
       <c r="K29">
-        <v>-212904.73964062484</v>
+        <v>-0.30515684832085144</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2748,7 +2803,7 @@
         <v>8760</v>
       </c>
       <c r="N29">
-        <v>612.0</v>
+        <v>392.0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2779,19 +2834,19 @@
         <v>8760</v>
       </c>
       <c r="V29">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W29">
-        <v>0.7062302728494009</v>
+        <v>0.8294468224048615</v>
       </c>
       <c r="X29">
-        <v>0.7172626063363738</v>
+        <v>0.8296518009049669</v>
       </c>
       <c r="Y29">
-        <v>0.4379631578922272</v>
+        <v>0.7087990045547485</v>
       </c>
       <c r="Z29">
-        <v>0.9300246238708496</v>
+        <v>0.9500946402549744</v>
       </c>
     </row>
     <row r="30">
@@ -2802,7 +2857,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B1051</t>
+          <t>B1052</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2811,28 +2866,28 @@
         </is>
       </c>
       <c r="D30">
-        <v>237.23200376810422</v>
+        <v>372.25901245316396</v>
       </c>
       <c r="E30">
-        <v>243.08</v>
+        <v>376.79</v>
       </c>
       <c r="F30">
-        <v>237.23</v>
+        <v>372.26</v>
       </c>
       <c r="G30">
-        <v>583179.328375</v>
+        <v>897705.558875</v>
       </c>
       <c r="H30">
-        <v>377373.86999999895</v>
+        <v>597127.5499999996</v>
       </c>
       <c r="I30">
-        <v>307207.1299999999</v>
+        <v>588688.6000000001</v>
       </c>
       <c r="J30">
-        <v>-275972.19837500015</v>
+        <v>-0.3442297486296714</v>
       </c>
       <c r="K30">
-        <v>-205805.4583750011</v>
+        <v>-0.3348291718853599</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2843,7 +2898,7 @@
         <v>8760</v>
       </c>
       <c r="N30">
-        <v>392.0</v>
+        <v>613.0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2877,16 +2932,16 @@
         <v>2.0</v>
       </c>
       <c r="W30">
-        <v>0.8294468224048615</v>
+        <v>0.9016911089420319</v>
       </c>
       <c r="X30">
-        <v>0.8296410093300808</v>
+        <v>0.9064905634024182</v>
       </c>
       <c r="Y30">
-        <v>0.7087990045547485</v>
+        <v>0.8705822825431824</v>
       </c>
       <c r="Z30">
-        <v>0.9500946402549744</v>
+        <v>0.9327999353408813</v>
       </c>
     </row>
     <row r="31">
@@ -2897,7 +2952,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B1052</t>
+          <t>B1053</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2906,28 +2961,28 @@
         </is>
       </c>
       <c r="D31">
-        <v>372.25901245316396</v>
+        <v>235.89975493456654</v>
       </c>
       <c r="E31">
-        <v>435.84</v>
+        <v>239.93</v>
       </c>
       <c r="F31">
-        <v>372.26</v>
+        <v>235.9</v>
       </c>
       <c r="G31">
-        <v>766199.57140625</v>
+        <v>572696.5886875</v>
       </c>
       <c r="H31">
-        <v>645703.4999999992</v>
+        <v>403176.09999999974</v>
       </c>
       <c r="I31">
-        <v>533110.0799999988</v>
+        <v>402532.75999999995</v>
       </c>
       <c r="J31">
-        <v>-233089.4914062512</v>
+        <v>-0.29712736560467334</v>
       </c>
       <c r="K31">
-        <v>-120496.07140625082</v>
+        <v>-0.2960040133572395</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2938,7 +2993,7 @@
         <v>8760</v>
       </c>
       <c r="N31">
-        <v>611.0</v>
+        <v>389.0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2972,16 +3027,16 @@
         <v>2.0</v>
       </c>
       <c r="W31">
-        <v>0.9016911089420319</v>
+        <v>0.9866441488265991</v>
       </c>
       <c r="X31">
-        <v>0.9016989735309956</v>
+        <v>0.9866730437575632</v>
       </c>
       <c r="Y31">
-        <v>0.8705822825431824</v>
+        <v>0.9758704900741577</v>
       </c>
       <c r="Z31">
-        <v>0.9327999353408813</v>
+        <v>0.9974178075790405</v>
       </c>
     </row>
     <row r="32">
@@ -2992,7 +3047,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B1053</t>
+          <t>B1054</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3001,28 +3056,28 @@
         </is>
       </c>
       <c r="D32">
-        <v>235.89975493456654</v>
+        <v>372.87641404951376</v>
       </c>
       <c r="E32">
-        <v>240.43</v>
+        <v>379.27</v>
       </c>
       <c r="F32">
-        <v>235.9</v>
+        <v>372.88</v>
       </c>
       <c r="G32">
-        <v>451117.05615625</v>
+        <v>858762.7599375</v>
       </c>
       <c r="H32">
-        <v>374201.11999999976</v>
+        <v>581726.9200000005</v>
       </c>
       <c r="I32">
-        <v>374485.57999999955</v>
+        <v>634476.1899999996</v>
       </c>
       <c r="J32">
-        <v>-76631.47615625046</v>
+        <v>-0.26117407554307986</v>
       </c>
       <c r="K32">
-        <v>-76915.93615625025</v>
+        <v>-0.3225988047707867</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3033,7 +3088,7 @@
         <v>8760</v>
       </c>
       <c r="N32">
-        <v>389.0</v>
+        <v>613.0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3064,19 +3119,19 @@
         <v>8760</v>
       </c>
       <c r="V32">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W32">
-        <v>0.9866441488265991</v>
+        <v>0.8530632853507996</v>
       </c>
       <c r="X32">
-        <v>0.9866594360559009</v>
+        <v>0.8530632853507996</v>
       </c>
       <c r="Y32">
-        <v>0.9758704900741577</v>
+        <v>0.8530632853507996</v>
       </c>
       <c r="Z32">
-        <v>0.9974178075790405</v>
+        <v>0.8530632853507996</v>
       </c>
     </row>
     <row r="33">
@@ -3087,7 +3142,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B1054</t>
+          <t>B1055</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3096,28 +3151,28 @@
         </is>
       </c>
       <c r="D33">
-        <v>372.87641404951376</v>
+        <v>238.60140604129373</v>
       </c>
       <c r="E33">
-        <v>437.96</v>
+        <v>243.47</v>
       </c>
       <c r="F33">
-        <v>372.88</v>
+        <v>238.6</v>
       </c>
       <c r="G33">
-        <v>754922.39365625</v>
+        <v>586904.6228125</v>
       </c>
       <c r="H33">
-        <v>638940.7300000006</v>
+        <v>397755.0000000008</v>
       </c>
       <c r="I33">
-        <v>594506.8599999998</v>
+        <v>400110.34000000067</v>
       </c>
       <c r="J33">
-        <v>-160415.53365625022</v>
+        <v>-0.3182702530393512</v>
       </c>
       <c r="K33">
-        <v>-115981.66365624941</v>
+        <v>-0.322283409365694</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3128,7 +3183,7 @@
         <v>8760</v>
       </c>
       <c r="N33">
-        <v>613.0</v>
+        <v>393.0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3159,19 +3214,19 @@
         <v>8760</v>
       </c>
       <c r="V33">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W33">
-        <v>0.8530632853507996</v>
+        <v>0.9899944961071014</v>
       </c>
       <c r="X33">
-        <v>0.8530632853507996</v>
+        <v>0.9899965978240969</v>
       </c>
       <c r="Y33">
-        <v>0.8530632853507996</v>
+        <v>0.9830652475357056</v>
       </c>
       <c r="Z33">
-        <v>0.8530632853507996</v>
+        <v>0.9969237446784973</v>
       </c>
     </row>
     <row r="34">
@@ -3182,7 +3237,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B1055</t>
+          <t>B1056</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3191,28 +3246,28 @@
         </is>
       </c>
       <c r="D34">
-        <v>238.60140604129373</v>
+        <v>369.61348279181516</v>
       </c>
       <c r="E34">
-        <v>243.81</v>
+        <v>379.78</v>
       </c>
       <c r="F34">
-        <v>238.6</v>
+        <v>369.61</v>
       </c>
       <c r="G34">
-        <v>585779.227875</v>
+        <v>898239.93771875</v>
       </c>
       <c r="H34">
-        <v>371699.8700000003</v>
+        <v>630150.38</v>
       </c>
       <c r="I34">
-        <v>376704.03999999986</v>
+        <v>625517.9499999981</v>
       </c>
       <c r="J34">
-        <v>-209075.18787500012</v>
+        <v>-0.30361819405556706</v>
       </c>
       <c r="K34">
-        <v>-214079.3578749997</v>
+        <v>-0.29846096400435507</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3223,7 +3278,7 @@
         <v>8760</v>
       </c>
       <c r="N34">
-        <v>394.0</v>
+        <v>610.0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3254,19 +3309,19 @@
         <v>8760</v>
       </c>
       <c r="V34">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W34">
-        <v>0.9899944961071014</v>
+        <v>0.7704202234745026</v>
       </c>
       <c r="X34">
-        <v>0.9899998184288374</v>
+        <v>0.7741709593541907</v>
       </c>
       <c r="Y34">
-        <v>0.9830652475357056</v>
+        <v>0.5520116090774536</v>
       </c>
       <c r="Z34">
-        <v>0.9969237446784973</v>
+        <v>0.9342544078826904</v>
       </c>
     </row>
     <row r="35">
@@ -3277,7 +3332,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B1056</t>
+          <t>B1057</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3286,28 +3341,28 @@
         </is>
       </c>
       <c r="D35">
-        <v>369.61348279181516</v>
+        <v>1996.1700056317245</v>
       </c>
       <c r="E35">
-        <v>437.15</v>
+        <v>1984.81</v>
       </c>
       <c r="F35">
-        <v>369.61</v>
+        <v>1984.81</v>
       </c>
       <c r="G35">
-        <v>855669.69303125</v>
+        <v>5424386.1137500005</v>
       </c>
       <c r="H35">
-        <v>678063.0299999987</v>
+        <v>3411092.7000000007</v>
       </c>
       <c r="I35">
-        <v>585688.0000000015</v>
+        <v>3412434.8700000052</v>
       </c>
       <c r="J35">
-        <v>-269981.6930312485</v>
+        <v>-0.3709085602608565</v>
       </c>
       <c r="K35">
-        <v>-177606.6630312513</v>
+        <v>-0.3711559928683183</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3318,7 +3373,7 @@
         <v>8760</v>
       </c>
       <c r="N35">
-        <v>611.0</v>
+        <v>3293.0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3347,21 +3402,6 @@
       </c>
       <c r="U35">
         <v>8760</v>
-      </c>
-      <c r="V35">
-        <v>4.0</v>
-      </c>
-      <c r="W35">
-        <v>0.7704202234745026</v>
-      </c>
-      <c r="X35">
-        <v>0.7705059363045601</v>
-      </c>
-      <c r="Y35">
-        <v>0.5520116090774536</v>
-      </c>
-      <c r="Z35">
-        <v>0.9342544078826904</v>
       </c>
     </row>
     <row r="36">
@@ -3372,7 +3412,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B1057</t>
+          <t>B1061</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3381,28 +3421,28 @@
         </is>
       </c>
       <c r="D36">
-        <v>1996.1700056317245</v>
+        <v>124.26560305683645</v>
       </c>
       <c r="E36">
-        <v>1984.81</v>
+        <v>126.24</v>
       </c>
       <c r="F36">
-        <v>1984.81</v>
+        <v>124.23</v>
       </c>
       <c r="G36">
-        <v>5404929.7555</v>
+        <v>264982.38575</v>
       </c>
       <c r="H36">
-        <v>3176662.629999991</v>
+        <v>225453.62999999936</v>
       </c>
       <c r="I36">
-        <v>3178126.1100000064</v>
+        <v>210540.3000000003</v>
       </c>
       <c r="J36">
-        <v>-2226803.6454999936</v>
+        <v>-0.20545548941265696</v>
       </c>
       <c r="K36">
-        <v>-2228267.125500009</v>
+        <v>-0.1491750315332069</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3413,7 +3453,7 @@
         <v>8760</v>
       </c>
       <c r="N36">
-        <v>3289.0</v>
+        <v>206.0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3442,6 +3482,21 @@
       </c>
       <c r="U36">
         <v>8760</v>
+      </c>
+      <c r="V36">
+        <v>1.0</v>
+      </c>
+      <c r="W36">
+        <v>0.9350892305374146</v>
+      </c>
+      <c r="X36">
+        <v>0.9350892305374146</v>
+      </c>
+      <c r="Y36">
+        <v>0.9350892305374146</v>
+      </c>
+      <c r="Z36">
+        <v>0.9350892305374146</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3507,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B1061</t>
+          <t>B1062</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3461,28 +3516,28 @@
         </is>
       </c>
       <c r="D37">
-        <v>124.26560305683645</v>
+        <v>123.18186977450087</v>
       </c>
       <c r="E37">
-        <v>126.66</v>
+        <v>125.03</v>
       </c>
       <c r="F37">
-        <v>124.23</v>
+        <v>123.17</v>
       </c>
       <c r="G37">
-        <v>182856.72184375</v>
+        <v>277058.5811875</v>
       </c>
       <c r="H37">
-        <v>205103.05000000037</v>
+        <v>181634.44999999987</v>
       </c>
       <c r="I37">
-        <v>195158.58999999976</v>
+        <v>185055.21000000034</v>
       </c>
       <c r="J37">
-        <v>12301.868156249751</v>
+        <v>-0.33207190621262933</v>
       </c>
       <c r="K37">
-        <v>22246.328156250354</v>
+        <v>-0.34441860915660155</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3493,7 +3548,7 @@
         <v>8760</v>
       </c>
       <c r="N37">
-        <v>203.0</v>
+        <v>202.0</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3524,19 +3579,19 @@
         <v>8760</v>
       </c>
       <c r="V37">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W37">
-        <v>0.9350892305374146</v>
+        <v>0.7779085437456766</v>
       </c>
       <c r="X37">
-        <v>0.9350892305374146</v>
+        <v>0.7575092045177529</v>
       </c>
       <c r="Y37">
-        <v>0.9350892305374146</v>
+        <v>0.6722833514213562</v>
       </c>
       <c r="Z37">
-        <v>0.9350892305374146</v>
+        <v>0.9671885371208191</v>
       </c>
     </row>
     <row r="38">
@@ -3547,7 +3602,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B1062</t>
+          <t>B1063</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3556,28 +3611,28 @@
         </is>
       </c>
       <c r="D38">
-        <v>123.18186977450087</v>
+        <v>123.35449520521844</v>
       </c>
       <c r="E38">
-        <v>125.54</v>
+        <v>125.03</v>
       </c>
       <c r="F38">
-        <v>123.17</v>
+        <v>123.35</v>
       </c>
       <c r="G38">
-        <v>201118.711375</v>
+        <v>279505.0353125</v>
       </c>
       <c r="H38">
-        <v>164574.21000000017</v>
+        <v>206213.97000000012</v>
       </c>
       <c r="I38">
-        <v>169032.97999999963</v>
+        <v>208929.51000000114</v>
       </c>
       <c r="J38">
-        <v>-32085.73137500038</v>
+        <v>-0.25250180281579565</v>
       </c>
       <c r="K38">
-        <v>-36544.50137499985</v>
+        <v>-0.26221733440528894</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3619,19 +3674,19 @@
         <v>8760</v>
       </c>
       <c r="V38">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W38">
-        <v>0.7779085437456766</v>
+        <v>0.6666513085365295</v>
       </c>
       <c r="X38">
-        <v>0.757241165727995</v>
+        <v>0.6666460422440421</v>
       </c>
       <c r="Y38">
-        <v>0.6722833514213562</v>
+        <v>0.6264314651489258</v>
       </c>
       <c r="Z38">
-        <v>0.9671885371208191</v>
+        <v>0.7068711519241333</v>
       </c>
     </row>
     <row r="39">
@@ -3642,7 +3697,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B1063</t>
+          <t>B1064</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3651,28 +3706,28 @@
         </is>
       </c>
       <c r="D39">
-        <v>123.35449520521844</v>
+        <v>122.91209748219146</v>
       </c>
       <c r="E39">
-        <v>125.44</v>
+        <v>122.91</v>
       </c>
       <c r="F39">
-        <v>123.35</v>
+        <v>122.91</v>
       </c>
       <c r="G39">
-        <v>207750.69015625</v>
+        <v>247551.24514062502</v>
       </c>
       <c r="H39">
-        <v>190831.2999999997</v>
+        <v>210503.4900000006</v>
       </c>
       <c r="I39">
-        <v>194056.90000000014</v>
+        <v>210232.2200000003</v>
       </c>
       <c r="J39">
-        <v>-13693.79015624986</v>
+        <v>-0.15075272644831628</v>
       </c>
       <c r="K39">
-        <v>-16919.3901562503</v>
+        <v>-0.1496569129336389</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3683,7 +3738,7 @@
         <v>8760</v>
       </c>
       <c r="N39">
-        <v>204.0</v>
+        <v>202.0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3712,21 +3767,6 @@
       </c>
       <c r="U39">
         <v>8760</v>
-      </c>
-      <c r="V39">
-        <v>2.0</v>
-      </c>
-      <c r="W39">
-        <v>0.6666513085365295</v>
-      </c>
-      <c r="X39">
-        <v>0.6666403712587918</v>
-      </c>
-      <c r="Y39">
-        <v>0.6264314651489258</v>
-      </c>
-      <c r="Z39">
-        <v>0.7068711519241333</v>
       </c>
     </row>
     <row r="40">
@@ -3737,7 +3777,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B1064</t>
+          <t>B1065</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3746,28 +3786,28 @@
         </is>
       </c>
       <c r="D40">
-        <v>122.91209748219146</v>
+        <v>121.72871093484056</v>
       </c>
       <c r="E40">
-        <v>122.91</v>
+        <v>126.23</v>
       </c>
       <c r="F40">
-        <v>122.91</v>
+        <v>121.73</v>
       </c>
       <c r="G40">
-        <v>168064.639015625</v>
+        <v>235608.508375</v>
       </c>
       <c r="H40">
-        <v>195629.09000000008</v>
+        <v>187501.68000000023</v>
       </c>
       <c r="I40">
-        <v>195691.39999999985</v>
+        <v>175662.0400000003</v>
       </c>
       <c r="J40">
-        <v>27626.76098437485</v>
+        <v>-0.25443252787623233</v>
       </c>
       <c r="K40">
-        <v>27564.450984375086</v>
+        <v>-0.2041812017180289</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3808,6 +3848,21 @@
       <c r="U40">
         <v>8760</v>
       </c>
+      <c r="V40">
+        <v>2.0</v>
+      </c>
+      <c r="W40">
+        <v>0.9834159016609192</v>
+      </c>
+      <c r="X40">
+        <v>0.9834990528412552</v>
+      </c>
+      <c r="Y40">
+        <v>0.967885434627533</v>
+      </c>
+      <c r="Z40">
+        <v>0.9989463686943054</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3817,7 +3872,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B1065</t>
+          <t>B1066</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3826,28 +3881,28 @@
         </is>
       </c>
       <c r="D41">
-        <v>121.72871093484056</v>
+        <v>120.87717554136132</v>
       </c>
       <c r="E41">
-        <v>126.67</v>
+        <v>123.74</v>
       </c>
       <c r="F41">
-        <v>121.73</v>
+        <v>120.88</v>
       </c>
       <c r="G41">
-        <v>184110.0953125</v>
+        <v>269707.395125</v>
       </c>
       <c r="H41">
-        <v>175268.00000000003</v>
+        <v>204377.80999999947</v>
       </c>
       <c r="I41">
-        <v>165352.3099999997</v>
+        <v>198508.96000000017</v>
       </c>
       <c r="J41">
-        <v>-18757.785312500288</v>
+        <v>-0.2639839930677534</v>
       </c>
       <c r="K41">
-        <v>-8842.095312499965</v>
+        <v>-0.2422239297321548</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3858,7 +3913,7 @@
         <v>8760</v>
       </c>
       <c r="N41">
-        <v>200.0</v>
+        <v>198.0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3892,16 +3947,16 @@
         <v>2.0</v>
       </c>
       <c r="W41">
-        <v>0.9834159016609192</v>
+        <v>0.9046740233898163</v>
       </c>
       <c r="X41">
-        <v>0.9835076080803388</v>
+        <v>0.9050082442125046</v>
       </c>
       <c r="Y41">
-        <v>0.967885434627533</v>
+        <v>0.8122680187225342</v>
       </c>
       <c r="Z41">
-        <v>0.9989463686943054</v>
+        <v>0.9970800280570984</v>
       </c>
     </row>
     <row r="42">
@@ -3912,7 +3967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B1066</t>
+          <t>B1067</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3921,28 +3976,28 @@
         </is>
       </c>
       <c r="D42">
-        <v>120.87717554136132</v>
+        <v>120.0414937883839</v>
       </c>
       <c r="E42">
-        <v>124.2</v>
+        <v>122.3</v>
       </c>
       <c r="F42">
-        <v>120.88</v>
+        <v>120.04</v>
       </c>
       <c r="G42">
-        <v>233059.40540625</v>
+        <v>270018.56453125</v>
       </c>
       <c r="H42">
-        <v>189216.53999999995</v>
+        <v>205338.3100000007</v>
       </c>
       <c r="I42">
-        <v>181583.96999999997</v>
+        <v>204199.00000000052</v>
       </c>
       <c r="J42">
-        <v>-51475.435406250035</v>
+        <v>-0.24375940463764662</v>
       </c>
       <c r="K42">
-        <v>-43842.86540625006</v>
+        <v>-0.2395400280848603</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3953,7 +4008,7 @@
         <v>8760</v>
       </c>
       <c r="N42">
-        <v>201.0</v>
+        <v>197.0</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3987,16 +4042,16 @@
         <v>2.0</v>
       </c>
       <c r="W42">
-        <v>0.9046740233898163</v>
+        <v>0.8856760263442993</v>
       </c>
       <c r="X42">
-        <v>0.9050908947596765</v>
+        <v>0.8858963498418937</v>
       </c>
       <c r="Y42">
-        <v>0.8122680187225342</v>
+        <v>0.778390109539032</v>
       </c>
       <c r="Z42">
-        <v>0.9970800280570984</v>
+        <v>0.9929619431495667</v>
       </c>
     </row>
     <row r="43">
@@ -4007,7 +4062,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B1067</t>
+          <t>B1068</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4016,28 +4071,28 @@
         </is>
       </c>
       <c r="D43">
-        <v>120.0414937883839</v>
+        <v>121.04616705044249</v>
       </c>
       <c r="E43">
-        <v>122.78</v>
+        <v>123.11</v>
       </c>
       <c r="F43">
-        <v>120.04</v>
+        <v>121.07</v>
       </c>
       <c r="G43">
-        <v>231558.52409375</v>
+        <v>276318.81809375</v>
       </c>
       <c r="H43">
-        <v>191076.29000000033</v>
+        <v>206467.07000000007</v>
       </c>
       <c r="I43">
-        <v>189473.2100000001</v>
+        <v>205750.07000000015</v>
       </c>
       <c r="J43">
-        <v>-42085.31409374988</v>
+        <v>-0.25538886052200443</v>
       </c>
       <c r="K43">
-        <v>-40482.23409374966</v>
+        <v>-0.2527940318203391</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4048,7 +4103,7 @@
         <v>8760</v>
       </c>
       <c r="N43">
-        <v>197.0</v>
+        <v>202.0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4082,16 +4137,16 @@
         <v>2.0</v>
       </c>
       <c r="W43">
-        <v>0.8856760263442993</v>
+        <v>0.9297216236591339</v>
       </c>
       <c r="X43">
-        <v>0.8858199301612759</v>
+        <v>0.9297205351581003</v>
       </c>
       <c r="Y43">
-        <v>0.778390109539032</v>
+        <v>0.921430230140686</v>
       </c>
       <c r="Z43">
-        <v>0.9929619431495667</v>
+        <v>0.9380130171775818</v>
       </c>
     </row>
     <row r="44">
@@ -4102,7 +4157,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B1068</t>
+          <t>B1069</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4111,28 +4166,28 @@
         </is>
       </c>
       <c r="D44">
-        <v>121.04616705044249</v>
+        <v>125.47070361249024</v>
       </c>
       <c r="E44">
-        <v>123.5</v>
+        <v>127.4</v>
       </c>
       <c r="F44">
-        <v>121.07</v>
+        <v>125.48</v>
       </c>
       <c r="G44">
-        <v>235315.61106250001</v>
+        <v>275909.47353125</v>
       </c>
       <c r="H44">
-        <v>192539.12999999986</v>
+        <v>216238.72000000006</v>
       </c>
       <c r="I44">
-        <v>191020.2100000001</v>
+        <v>215600.3699999995</v>
       </c>
       <c r="J44">
-        <v>-44295.40106249991</v>
+        <v>-0.21858293866962783</v>
       </c>
       <c r="K44">
-        <v>-42776.481062500156</v>
+        <v>-0.21626931749587622</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4143,7 +4198,7 @@
         <v>8760</v>
       </c>
       <c r="N44">
-        <v>199.0</v>
+        <v>206.0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4177,16 +4232,16 @@
         <v>2.0</v>
       </c>
       <c r="W44">
-        <v>0.9297216236591339</v>
+        <v>0.851101279258728</v>
       </c>
       <c r="X44">
-        <v>0.9297216503157362</v>
+        <v>0.8510582489557049</v>
       </c>
       <c r="Y44">
-        <v>0.921430230140686</v>
+        <v>0.7123515605926514</v>
       </c>
       <c r="Z44">
-        <v>0.9380130171775818</v>
+        <v>0.9898509979248047</v>
       </c>
     </row>
     <row r="45">
@@ -4197,7 +4252,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B1069</t>
+          <t>B1070</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4206,28 +4261,28 @@
         </is>
       </c>
       <c r="D45">
-        <v>125.47070361249024</v>
+        <v>116.75256223313664</v>
       </c>
       <c r="E45">
-        <v>127.86</v>
+        <v>118.57</v>
       </c>
       <c r="F45">
-        <v>125.48</v>
+        <v>116.75</v>
       </c>
       <c r="G45">
-        <v>251390.657828125</v>
+        <v>279143.835625</v>
       </c>
       <c r="H45">
-        <v>202162.71999999922</v>
+        <v>201668.6000000004</v>
       </c>
       <c r="I45">
-        <v>200876.83000000037</v>
+        <v>199929.34999999977</v>
       </c>
       <c r="J45">
-        <v>-50513.82782812463</v>
+        <v>-0.28377658939750494</v>
       </c>
       <c r="K45">
-        <v>-49227.93782812578</v>
+        <v>-0.2775459305828244</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4238,7 +4293,7 @@
         <v>8760</v>
       </c>
       <c r="N45">
-        <v>208.0</v>
+        <v>193.0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4272,16 +4327,16 @@
         <v>2.0</v>
       </c>
       <c r="W45">
-        <v>0.851101279258728</v>
+        <v>0.8419512808322906</v>
       </c>
       <c r="X45">
-        <v>0.8512757968970323</v>
+        <v>0.8418828661570861</v>
       </c>
       <c r="Y45">
-        <v>0.7123515605926514</v>
+        <v>0.7161607146263123</v>
       </c>
       <c r="Z45">
-        <v>0.9898509979248047</v>
+        <v>0.967741847038269</v>
       </c>
     </row>
     <row r="46">
@@ -4292,7 +4347,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B1070</t>
+          <t>B1071</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4301,28 +4356,28 @@
         </is>
       </c>
       <c r="D46">
-        <v>116.75256223313664</v>
+        <v>124.10312756987287</v>
       </c>
       <c r="E46">
-        <v>118.99</v>
+        <v>125.9</v>
       </c>
       <c r="F46">
-        <v>116.75</v>
+        <v>124.1</v>
       </c>
       <c r="G46">
-        <v>250564.03903125</v>
+        <v>291034.884875</v>
       </c>
       <c r="H46">
-        <v>188423.85999999996</v>
+        <v>214372.36999999982</v>
       </c>
       <c r="I46">
-        <v>185929.51000000015</v>
+        <v>214446.27999999915</v>
       </c>
       <c r="J46">
-        <v>-64634.52903124984</v>
+        <v>-0.26315953466504804</v>
       </c>
       <c r="K46">
-        <v>-62140.17903125004</v>
+        <v>-0.26341349047529766</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4333,7 +4388,7 @@
         <v>8760</v>
       </c>
       <c r="N46">
-        <v>194.0</v>
+        <v>205.0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4367,16 +4422,16 @@
         <v>2.0</v>
       </c>
       <c r="W46">
-        <v>0.8419512808322906</v>
+        <v>0.7650662958621979</v>
       </c>
       <c r="X46">
-        <v>0.8421040957406822</v>
+        <v>0.7650008274414574</v>
       </c>
       <c r="Y46">
-        <v>0.7161607146263123</v>
+        <v>0.6473265886306763</v>
       </c>
       <c r="Z46">
-        <v>0.967741847038269</v>
+        <v>0.8828060030937195</v>
       </c>
     </row>
     <row r="47">
@@ -4387,7 +4442,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B1071</t>
+          <t>B1072</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4396,28 +4451,28 @@
         </is>
       </c>
       <c r="D47">
-        <v>124.10312756987287</v>
+        <v>130.9085264508188</v>
       </c>
       <c r="E47">
-        <v>126.54</v>
+        <v>132.72</v>
       </c>
       <c r="F47">
-        <v>124.1</v>
+        <v>130.92</v>
       </c>
       <c r="G47">
-        <v>262935.11865625</v>
+        <v>292941.29778125003</v>
       </c>
       <c r="H47">
-        <v>200488.56000000032</v>
+        <v>224439.10000000018</v>
       </c>
       <c r="I47">
-        <v>199699.34000000005</v>
+        <v>223754.9800000001</v>
       </c>
       <c r="J47">
-        <v>-63235.77865624995</v>
+        <v>-0.23617809542481746</v>
       </c>
       <c r="K47">
-        <v>-62446.55865624969</v>
+        <v>-0.23384274699432425</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4428,7 +4483,7 @@
         <v>8760</v>
       </c>
       <c r="N47">
-        <v>205.0</v>
+        <v>214.0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4462,16 +4517,16 @@
         <v>2.0</v>
       </c>
       <c r="W47">
-        <v>0.7650662958621979</v>
+        <v>0.8466036021709442</v>
       </c>
       <c r="X47">
-        <v>0.7651136333067663</v>
+        <v>0.8466980929066061</v>
       </c>
       <c r="Y47">
-        <v>0.6473265886306763</v>
+        <v>0.7241121530532837</v>
       </c>
       <c r="Z47">
-        <v>0.8828060030937195</v>
+        <v>0.9690950512886047</v>
       </c>
     </row>
     <row r="48">
@@ -4482,7 +4537,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B1072</t>
+          <t>B1073</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4491,28 +4546,28 @@
         </is>
       </c>
       <c r="D48">
-        <v>130.9085264508188</v>
+        <v>118.41081365152584</v>
       </c>
       <c r="E48">
-        <v>132.99</v>
+        <v>121.09</v>
       </c>
       <c r="F48">
-        <v>130.92</v>
+        <v>118.44</v>
       </c>
       <c r="G48">
-        <v>281591.344</v>
+        <v>281187.1920625</v>
       </c>
       <c r="H48">
-        <v>209111.72999999946</v>
+        <v>205150.85999999952</v>
       </c>
       <c r="I48">
-        <v>208057.14000000028</v>
+        <v>200779.8799999999</v>
       </c>
       <c r="J48">
-        <v>-73534.2039999997</v>
+        <v>-0.285956524095976</v>
       </c>
       <c r="K48">
-        <v>-72479.61400000053</v>
+        <v>-0.2704117904687484</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4523,7 +4578,7 @@
         <v>8760</v>
       </c>
       <c r="N48">
-        <v>217.0</v>
+        <v>195.0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4557,16 +4612,16 @@
         <v>2.0</v>
       </c>
       <c r="W48">
-        <v>0.8466036021709442</v>
+        <v>0.8725321888923645</v>
       </c>
       <c r="X48">
-        <v>0.8466988649521602</v>
+        <v>0.8730019373729163</v>
       </c>
       <c r="Y48">
-        <v>0.7241121530532837</v>
+        <v>0.762785792350769</v>
       </c>
       <c r="Z48">
-        <v>0.9690950512886047</v>
+        <v>0.98227858543396</v>
       </c>
     </row>
     <row r="49">
@@ -4577,7 +4632,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B1073</t>
+          <t>B1074</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4586,28 +4641,28 @@
         </is>
       </c>
       <c r="D49">
-        <v>118.41081365152584</v>
+        <v>112.27774131099156</v>
       </c>
       <c r="E49">
-        <v>121.5</v>
+        <v>113.83</v>
       </c>
       <c r="F49">
-        <v>118.44</v>
+        <v>112.23</v>
       </c>
       <c r="G49">
-        <v>249276.57103125</v>
+        <v>215944.514375</v>
       </c>
       <c r="H49">
-        <v>190934.8600000002</v>
+        <v>176188.7200000002</v>
       </c>
       <c r="I49">
-        <v>186691.0800000006</v>
+        <v>193890.17000000048</v>
       </c>
       <c r="J49">
-        <v>-62585.4910312494</v>
+        <v>-0.10212968103788407</v>
       </c>
       <c r="K49">
-        <v>-58341.71103124981</v>
+        <v>-0.18410189529501816</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4618,7 +4673,7 @@
         <v>8760</v>
       </c>
       <c r="N49">
-        <v>193.0</v>
+        <v>185.0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4649,19 +4704,19 @@
         <v>8760</v>
       </c>
       <c r="V49">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W49">
-        <v>0.8725321888923645</v>
+        <v>0.9849328398704529</v>
       </c>
       <c r="X49">
-        <v>0.8729938680975564</v>
+        <v>0.9849328398704529</v>
       </c>
       <c r="Y49">
-        <v>0.762785792350769</v>
+        <v>0.9849328398704529</v>
       </c>
       <c r="Z49">
-        <v>0.98227858543396</v>
+        <v>0.9849328398704529</v>
       </c>
     </row>
     <row r="50">
@@ -4672,7 +4727,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B1074</t>
+          <t>B1075</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4681,28 +4736,28 @@
         </is>
       </c>
       <c r="D50">
-        <v>112.27774131099156</v>
+        <v>57.314386881618</v>
       </c>
       <c r="E50">
-        <v>114.03</v>
+        <v>56.91</v>
       </c>
       <c r="F50">
-        <v>112.23</v>
+        <v>56.91</v>
       </c>
       <c r="G50">
-        <v>131818.98642187502</v>
+        <v>135464.283875</v>
       </c>
       <c r="H50">
-        <v>165270.40000000005</v>
+        <v>98060.66000000016</v>
       </c>
       <c r="I50">
-        <v>180153.30999999988</v>
+        <v>98379.99999999993</v>
       </c>
       <c r="J50">
-        <v>48334.323578124866</v>
+        <v>-0.2737569107826214</v>
       </c>
       <c r="K50">
-        <v>33451.41357812504</v>
+        <v>-0.2761142849248302</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4713,7 +4768,7 @@
         <v>8760</v>
       </c>
       <c r="N50">
-        <v>181.0</v>
+        <v>97.0</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4742,21 +4797,6 @@
       </c>
       <c r="U50">
         <v>8760</v>
-      </c>
-      <c r="V50">
-        <v>1.0</v>
-      </c>
-      <c r="W50">
-        <v>0.9849328398704529</v>
-      </c>
-      <c r="X50">
-        <v>0.9849328398704529</v>
-      </c>
-      <c r="Y50">
-        <v>0.9849328398704529</v>
-      </c>
-      <c r="Z50">
-        <v>0.9849328398704529</v>
       </c>
     </row>
     <row r="51">
@@ -4767,7 +4807,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B1075</t>
+          <t>B1076</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4776,28 +4816,28 @@
         </is>
       </c>
       <c r="D51">
-        <v>57.314386881618</v>
+        <v>110.62788457108744</v>
       </c>
       <c r="E51">
-        <v>56.91</v>
+        <v>112.3</v>
       </c>
       <c r="F51">
-        <v>56.91</v>
+        <v>110.6</v>
       </c>
       <c r="G51">
-        <v>139452.1359375</v>
+        <v>253369.3274375</v>
       </c>
       <c r="H51">
-        <v>91251.7800000004</v>
+        <v>191601.66000000056</v>
       </c>
       <c r="I51">
-        <v>91606.44999999985</v>
+        <v>191129.89000000016</v>
       </c>
       <c r="J51">
-        <v>-47845.68593750014</v>
+        <v>-0.24564708785775494</v>
       </c>
       <c r="K51">
-        <v>-48200.35593749958</v>
+        <v>-0.24378510241235105</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4808,7 +4848,7 @@
         <v>8760</v>
       </c>
       <c r="N51">
-        <v>97.0</v>
+        <v>182.0</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4837,6 +4877,21 @@
       </c>
       <c r="U51">
         <v>8760</v>
+      </c>
+      <c r="V51">
+        <v>2.0</v>
+      </c>
+      <c r="W51">
+        <v>0.9626638889312744</v>
+      </c>
+      <c r="X51">
+        <v>0.9626838051242314</v>
+      </c>
+      <c r="Y51">
+        <v>0.9442288279533386</v>
+      </c>
+      <c r="Z51">
+        <v>0.9810989499092102</v>
       </c>
     </row>
     <row r="52">
@@ -4847,7 +4902,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B1076</t>
+          <t>B1077</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4856,28 +4911,28 @@
         </is>
       </c>
       <c r="D52">
-        <v>110.62788457108744</v>
+        <v>58.5967501938149</v>
       </c>
       <c r="E52">
-        <v>112.62</v>
+        <v>61.21</v>
       </c>
       <c r="F52">
-        <v>110.6</v>
+        <v>58.6</v>
       </c>
       <c r="G52">
-        <v>235285.17587500002</v>
+        <v>119194.47425</v>
       </c>
       <c r="H52">
-        <v>178817.0799999999</v>
+        <v>106030.69000000006</v>
       </c>
       <c r="I52">
-        <v>178025.3699999999</v>
+        <v>100388.20999999973</v>
       </c>
       <c r="J52">
-        <v>-57259.80587500011</v>
+        <v>-0.1577779873465927</v>
       </c>
       <c r="K52">
-        <v>-56468.095875000115</v>
+        <v>-0.11043955126971784</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -4888,7 +4943,7 @@
         <v>8760</v>
       </c>
       <c r="N52">
-        <v>181.0</v>
+        <v>100.0</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4922,16 +4977,16 @@
         <v>2.0</v>
       </c>
       <c r="W52">
-        <v>0.9626638889312744</v>
+        <v>0.9952588081359863</v>
       </c>
       <c r="X52">
-        <v>0.962659387801195</v>
+        <v>0.9945255588123589</v>
       </c>
       <c r="Y52">
-        <v>0.9442288279533386</v>
+        <v>0.991319477558136</v>
       </c>
       <c r="Z52">
-        <v>0.9810989499092102</v>
+        <v>0.9991981387138367</v>
       </c>
     </row>
     <row r="53">
@@ -4942,7 +4997,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B1077</t>
+          <t>B1078</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4951,28 +5006,28 @@
         </is>
       </c>
       <c r="D53">
-        <v>58.5967501938149</v>
+        <v>119.07112961905189</v>
       </c>
       <c r="E53">
-        <v>72.75</v>
+        <v>122.2</v>
       </c>
       <c r="F53">
-        <v>58.6</v>
+        <v>119.05</v>
       </c>
       <c r="G53">
-        <v>67786.96169531251</v>
+        <v>267140.7060625</v>
       </c>
       <c r="H53">
-        <v>115280.16000000003</v>
+        <v>206125.56000000035</v>
       </c>
       <c r="I53">
-        <v>93698.79999999961</v>
+        <v>205752.11000000034</v>
       </c>
       <c r="J53">
-        <v>25911.838304687102</v>
+        <v>-0.22979873403545342</v>
       </c>
       <c r="K53">
-        <v>47493.198304687525</v>
+        <v>-0.22840078160242872</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4983,7 +5038,7 @@
         <v>8760</v>
       </c>
       <c r="N53">
-        <v>99.0</v>
+        <v>198.0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5017,16 +5072,16 @@
         <v>2.0</v>
       </c>
       <c r="W53">
-        <v>0.9952588081359863</v>
+        <v>0.843268871307373</v>
       </c>
       <c r="X53">
-        <v>0.9952446628721586</v>
+        <v>0.8438735427448264</v>
       </c>
       <c r="Y53">
-        <v>0.991319477558136</v>
+        <v>0.6907517313957214</v>
       </c>
       <c r="Z53">
-        <v>0.9991981387138367</v>
+        <v>0.9957860112190247</v>
       </c>
     </row>
     <row r="54">
@@ -5037,7 +5092,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B1078</t>
+          <t>B1079</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5046,28 +5101,28 @@
         </is>
       </c>
       <c r="D54">
-        <v>119.07112961905189</v>
+        <v>168.56033444445646</v>
       </c>
       <c r="E54">
-        <v>122.21</v>
+        <v>175.18</v>
       </c>
       <c r="F54">
-        <v>119.05</v>
+        <v>150.52</v>
       </c>
       <c r="G54">
-        <v>164543.363234375</v>
+        <v>361110.8783125</v>
       </c>
       <c r="H54">
-        <v>193298.3600000003</v>
+        <v>298728.4899999997</v>
       </c>
       <c r="I54">
-        <v>191564.84999999998</v>
+        <v>260199.59999999995</v>
       </c>
       <c r="J54">
-        <v>27021.486765624984</v>
+        <v>-0.27944679701721126</v>
       </c>
       <c r="K54">
-        <v>28754.996765625314</v>
+        <v>-0.17275134054121605</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -5078,7 +5133,7 @@
         <v>8760</v>
       </c>
       <c r="N54">
-        <v>196.0</v>
+        <v>276.0</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5112,16 +5167,16 @@
         <v>2.0</v>
       </c>
       <c r="W54">
-        <v>0.843268871307373</v>
+        <v>0.9855310320854187</v>
       </c>
       <c r="X54">
-        <v>0.8437860258821651</v>
+        <v>0.9856488374403087</v>
       </c>
       <c r="Y54">
-        <v>0.6907517313957214</v>
+        <v>0.9830591678619385</v>
       </c>
       <c r="Z54">
-        <v>0.9957860112190247</v>
+        <v>0.9880028963088989</v>
       </c>
     </row>
     <row r="55">
@@ -5132,7 +5187,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B1079</t>
+          <t>B1080</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5141,28 +5196,28 @@
         </is>
       </c>
       <c r="D55">
-        <v>168.56033444445646</v>
+        <v>56.743204455406456</v>
       </c>
       <c r="E55">
-        <v>183.59</v>
+        <v>58.18</v>
       </c>
       <c r="F55">
-        <v>150.52</v>
+        <v>56.74</v>
       </c>
       <c r="G55">
-        <v>342660.32071875</v>
+        <v>111803.671671875</v>
       </c>
       <c r="H55">
-        <v>292551.79000000056</v>
+        <v>101661.64999999989</v>
       </c>
       <c r="I55">
-        <v>242401.50999999957</v>
+        <v>96835.46000000015</v>
       </c>
       <c r="J55">
-        <v>-100258.81071875044</v>
+        <v>-0.1338794285379467</v>
       </c>
       <c r="K55">
-        <v>-50108.53071874945</v>
+        <v>-0.09071277821394126</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -5173,7 +5228,7 @@
         <v>8760</v>
       </c>
       <c r="N55">
-        <v>276.0</v>
+        <v>93.0</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5207,16 +5262,16 @@
         <v>2.0</v>
       </c>
       <c r="W55">
-        <v>0.9855310320854187</v>
+        <v>0.7142086029052734</v>
       </c>
       <c r="X55">
-        <v>0.9855314049810306</v>
+        <v>0.6614543163205797</v>
       </c>
       <c r="Y55">
-        <v>0.9830591678619385</v>
+        <v>0.4353100657463074</v>
       </c>
       <c r="Z55">
-        <v>0.9880028963088989</v>
+        <v>0.9931071400642395</v>
       </c>
     </row>
     <row r="56">
@@ -5227,7 +5282,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B1080</t>
+          <t>B1081</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5236,28 +5291,28 @@
         </is>
       </c>
       <c r="D56">
-        <v>56.743204455406456</v>
+        <v>55.444514960964774</v>
       </c>
       <c r="E56">
-        <v>69.39</v>
+        <v>55.44</v>
       </c>
       <c r="F56">
-        <v>56.74</v>
+        <v>55.44</v>
       </c>
       <c r="G56">
-        <v>57873.2223359375</v>
+        <v>103219.02082812501</v>
       </c>
       <c r="H56">
-        <v>112717.74999999975</v>
+        <v>96140.8800000004</v>
       </c>
       <c r="I56">
-        <v>90683.04000000024</v>
+        <v>95933.09000000003</v>
       </c>
       <c r="J56">
-        <v>32809.81766406274</v>
+        <v>-0.07058709499150491</v>
       </c>
       <c r="K56">
-        <v>54844.527664062254</v>
+        <v>-0.06857399703404246</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5268,7 +5323,7 @@
         <v>8760</v>
       </c>
       <c r="N56">
-        <v>93.0</v>
+        <v>91.0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5297,21 +5352,6 @@
       </c>
       <c r="U56">
         <v>8760</v>
-      </c>
-      <c r="V56">
-        <v>2.0</v>
-      </c>
-      <c r="W56">
-        <v>0.7142086029052734</v>
-      </c>
-      <c r="X56">
-        <v>0.7147609265401115</v>
-      </c>
-      <c r="Y56">
-        <v>0.4353100657463074</v>
-      </c>
-      <c r="Z56">
-        <v>0.9931071400642395</v>
       </c>
     </row>
     <row r="57">
@@ -5322,7 +5362,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B1081</t>
+          <t>B1082</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5331,28 +5371,28 @@
         </is>
       </c>
       <c r="D57">
-        <v>55.444514960964774</v>
+        <v>168.7324221607141</v>
       </c>
       <c r="E57">
-        <v>55.44</v>
+        <v>171.57</v>
       </c>
       <c r="F57">
-        <v>55.44</v>
+        <v>168.73</v>
       </c>
       <c r="G57">
-        <v>52518.1471171875</v>
+        <v>380573.5991171875</v>
       </c>
       <c r="H57">
-        <v>89310.13999999996</v>
+        <v>279210.8800000001</v>
       </c>
       <c r="I57">
-        <v>89402.86000000034</v>
+        <v>288784.7199999997</v>
       </c>
       <c r="J57">
-        <v>36884.71288281283</v>
+        <v>-0.24118561910261113</v>
       </c>
       <c r="K57">
-        <v>36791.992882812454</v>
+        <v>-0.26634196211276184</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5363,7 +5403,7 @@
         <v>8760</v>
       </c>
       <c r="N57">
-        <v>91.0</v>
+        <v>281.0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5392,6 +5432,21 @@
       </c>
       <c r="U57">
         <v>8760</v>
+      </c>
+      <c r="V57">
+        <v>2.0</v>
+      </c>
+      <c r="W57">
+        <v>0.5803835690021515</v>
+      </c>
+      <c r="X57">
+        <v>0.6315674323779735</v>
+      </c>
+      <c r="Y57">
+        <v>0.4520184397697449</v>
+      </c>
+      <c r="Z57">
+        <v>0.7087486982345581</v>
       </c>
     </row>
     <row r="58">
@@ -5402,7 +5457,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B1082</t>
+          <t>B1083</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5411,28 +5466,28 @@
         </is>
       </c>
       <c r="D58">
-        <v>168.7324221607141</v>
+        <v>168.60523585324364</v>
       </c>
       <c r="E58">
-        <v>261.93</v>
+        <v>168.61</v>
       </c>
       <c r="F58">
-        <v>168.73</v>
+        <v>168.61</v>
       </c>
       <c r="G58">
-        <v>267729.331890625</v>
+        <v>376216.25653125</v>
       </c>
       <c r="H58">
-        <v>413404.0100000002</v>
+        <v>291866.9499999996</v>
       </c>
       <c r="I58">
-        <v>270238.0900000001</v>
+        <v>291818.6400000003</v>
       </c>
       <c r="J58">
-        <v>2508.7581093750778</v>
+        <v>-0.22433272105092916</v>
       </c>
       <c r="K58">
-        <v>145674.67810937518</v>
+        <v>-0.22420431086354192</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5443,7 +5498,7 @@
         <v>8760</v>
       </c>
       <c r="N58">
-        <v>276.0</v>
+        <v>278.0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5472,21 +5527,6 @@
       </c>
       <c r="U58">
         <v>8760</v>
-      </c>
-      <c r="V58">
-        <v>2.0</v>
-      </c>
-      <c r="W58">
-        <v>0.5803835690021515</v>
-      </c>
-      <c r="X58">
-        <v>0.5803449371490812</v>
-      </c>
-      <c r="Y58">
-        <v>0.4520184397697449</v>
-      </c>
-      <c r="Z58">
-        <v>0.7087486982345581</v>
       </c>
     </row>
     <row r="59">
@@ -5497,7 +5537,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B1083</t>
+          <t>B1084</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5506,28 +5546,28 @@
         </is>
       </c>
       <c r="D59">
-        <v>168.60523585324364</v>
+        <v>111.8848157134316</v>
       </c>
       <c r="E59">
-        <v>168.61</v>
+        <v>115.02</v>
       </c>
       <c r="F59">
-        <v>168.61</v>
+        <v>111.85</v>
       </c>
       <c r="G59">
-        <v>283567.41364843753</v>
+        <v>259544.44775</v>
       </c>
       <c r="H59">
-        <v>271900.5200000004</v>
+        <v>194989.27999999994</v>
       </c>
       <c r="I59">
-        <v>272032.3599999995</v>
+        <v>193298.7399999995</v>
       </c>
       <c r="J59">
-        <v>-11535.053648438014</v>
+        <v>-0.2552383929777226</v>
       </c>
       <c r="K59">
-        <v>-11666.893648437108</v>
+        <v>-0.24872490361335442</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5538,7 +5578,7 @@
         <v>8760</v>
       </c>
       <c r="N59">
-        <v>278.0</v>
+        <v>187.0</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5567,6 +5607,21 @@
       </c>
       <c r="U59">
         <v>8760</v>
+      </c>
+      <c r="V59">
+        <v>2.0</v>
+      </c>
+      <c r="W59">
+        <v>0.9448669254779816</v>
+      </c>
+      <c r="X59">
+        <v>0.9448813437381243</v>
+      </c>
+      <c r="Y59">
+        <v>0.8904971480369568</v>
+      </c>
+      <c r="Z59">
+        <v>0.9992367029190063</v>
       </c>
     </row>
     <row r="60">
@@ -5577,7 +5632,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B1084</t>
+          <t>B1085</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5586,28 +5641,28 @@
         </is>
       </c>
       <c r="D60">
-        <v>111.8848157134316</v>
+        <v>109.86903584095278</v>
       </c>
       <c r="E60">
-        <v>115.11</v>
+        <v>110.58</v>
       </c>
       <c r="F60">
-        <v>111.85</v>
+        <v>109.87</v>
       </c>
       <c r="G60">
-        <v>235455.580125</v>
+        <v>272527.6270625</v>
       </c>
       <c r="H60">
-        <v>181154.76000000018</v>
+        <v>189821.53000000035</v>
       </c>
       <c r="I60">
-        <v>180168.88000000024</v>
+        <v>190048.94000000064</v>
       </c>
       <c r="J60">
-        <v>-55286.70012499977</v>
+        <v>-0.30264339785112554</v>
       </c>
       <c r="K60">
-        <v>-54300.820124999824</v>
+        <v>-0.30347784536182926</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5618,7 +5673,7 @@
         <v>8760</v>
       </c>
       <c r="N60">
-        <v>184.0</v>
+        <v>179.0</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5652,16 +5707,16 @@
         <v>2.0</v>
       </c>
       <c r="W60">
-        <v>0.9448669254779816</v>
+        <v>0.9668639302253723</v>
       </c>
       <c r="X60">
-        <v>0.9448649207578469</v>
+        <v>0.9668767547494551</v>
       </c>
       <c r="Y60">
-        <v>0.8904971480369568</v>
+        <v>0.9546698927879333</v>
       </c>
       <c r="Z60">
-        <v>0.9992367029190063</v>
+        <v>0.9790579676628113</v>
       </c>
     </row>
     <row r="61">
@@ -5672,7 +5727,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B1085</t>
+          <t>B1086</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5681,28 +5736,28 @@
         </is>
       </c>
       <c r="D61">
-        <v>109.86903584095278</v>
+        <v>451.4562124773123</v>
       </c>
       <c r="E61">
-        <v>110.86</v>
+        <v>451.33</v>
       </c>
       <c r="F61">
-        <v>109.87</v>
+        <v>451.46</v>
       </c>
       <c r="G61">
-        <v>251359.76537500002</v>
+        <v>910426.1154375001</v>
       </c>
       <c r="H61">
-        <v>176948.43000000008</v>
+        <v>782367.1599999971</v>
       </c>
       <c r="I61">
-        <v>177217.48</v>
+        <v>782867.660000003</v>
       </c>
       <c r="J61">
-        <v>-74142.285375</v>
+        <v>-0.1401085198178873</v>
       </c>
       <c r="K61">
-        <v>-74411.33537499994</v>
+        <v>-0.14065826239613627</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5713,7 +5768,7 @@
         <v>8760</v>
       </c>
       <c r="N61">
-        <v>180.0</v>
+        <v>744.0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5744,19 +5799,19 @@
         <v>8760</v>
       </c>
       <c r="V61">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W61">
-        <v>0.9668639302253723</v>
+        <v>0.969103991985321</v>
       </c>
       <c r="X61">
-        <v>0.9668605152885246</v>
+        <v>0.969103991985321</v>
       </c>
       <c r="Y61">
-        <v>0.9546698927879333</v>
+        <v>0.969103991985321</v>
       </c>
       <c r="Z61">
-        <v>0.9790579676628113</v>
+        <v>0.969103991985321</v>
       </c>
     </row>
     <row r="62">
@@ -5767,7 +5822,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B1086</t>
+          <t>B1087</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5776,28 +5831,28 @@
         </is>
       </c>
       <c r="D62">
-        <v>451.4562124773123</v>
+        <v>509.8186953937832</v>
       </c>
       <c r="E62">
-        <v>453.06</v>
+        <v>509.71</v>
       </c>
       <c r="F62">
-        <v>451.46</v>
+        <v>509.71</v>
       </c>
       <c r="G62">
-        <v>831375.4134062501</v>
+        <v>1083195.76996875</v>
       </c>
       <c r="H62">
-        <v>731803.509999998</v>
+        <v>883440.0500000028</v>
       </c>
       <c r="I62">
-        <v>730107.3899999983</v>
+        <v>884032.2200000017</v>
       </c>
       <c r="J62">
-        <v>-101268.0234062518</v>
+        <v>-0.18386662456639216</v>
       </c>
       <c r="K62">
-        <v>-99571.90340625204</v>
+        <v>-0.1844133124472135</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5808,7 +5863,7 @@
         <v>8760</v>
       </c>
       <c r="N62">
-        <v>744.0</v>
+        <v>840.0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5837,21 +5892,6 @@
       </c>
       <c r="U62">
         <v>8760</v>
-      </c>
-      <c r="V62">
-        <v>1.0</v>
-      </c>
-      <c r="W62">
-        <v>0.969103991985321</v>
-      </c>
-      <c r="X62">
-        <v>0.969103991985321</v>
-      </c>
-      <c r="Y62">
-        <v>0.969103991985321</v>
-      </c>
-      <c r="Z62">
-        <v>0.969103991985321</v>
       </c>
     </row>
     <row r="63">
@@ -5862,7 +5902,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B1087</t>
+          <t>B1088</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5871,28 +5911,28 @@
         </is>
       </c>
       <c r="D63">
-        <v>509.8186953937832</v>
+        <v>499.23426278892276</v>
       </c>
       <c r="E63">
-        <v>509.71</v>
+        <v>500.08</v>
       </c>
       <c r="F63">
-        <v>509.71</v>
+        <v>500.08</v>
       </c>
       <c r="G63">
-        <v>1115532.40621875</v>
+        <v>1062625.4551796876</v>
       </c>
       <c r="H63">
-        <v>823621.9299999994</v>
+        <v>862444.2100000001</v>
       </c>
       <c r="I63">
-        <v>824519.2000000008</v>
+        <v>861089.1999999991</v>
       </c>
       <c r="J63">
-        <v>-291013.20621874917</v>
+        <v>-0.18965878729642244</v>
       </c>
       <c r="K63">
-        <v>-291910.4762187506</v>
+        <v>-0.18838363433128685</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -5903,7 +5943,7 @@
         <v>8760</v>
       </c>
       <c r="N63">
-        <v>841.0</v>
+        <v>823.0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5942,7 +5982,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B1088</t>
+          <t>B1089</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5951,28 +5991,28 @@
         </is>
       </c>
       <c r="D64">
-        <v>499.23426278892276</v>
+        <v>471.0500449089885</v>
       </c>
       <c r="E64">
-        <v>500.08</v>
+        <v>471.05</v>
       </c>
       <c r="F64">
-        <v>500.08</v>
+        <v>471.05</v>
       </c>
       <c r="G64">
-        <v>1056202.90434375</v>
+        <v>1044686.848125</v>
       </c>
       <c r="H64">
-        <v>805096.3700000001</v>
+        <v>802377.9799999996</v>
       </c>
       <c r="I64">
-        <v>804082.1299999978</v>
+        <v>803482.4600000002</v>
       </c>
       <c r="J64">
-        <v>-252120.7743437523</v>
+        <v>-0.23088678541125748</v>
       </c>
       <c r="K64">
-        <v>-251106.53434374998</v>
+        <v>-0.23194402088998767</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -5983,7 +6023,7 @@
         <v>8760</v>
       </c>
       <c r="N64">
-        <v>824.0</v>
+        <v>777.0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6022,7 +6062,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B1089</t>
+          <t>B1091</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6031,28 +6071,28 @@
         </is>
       </c>
       <c r="D65">
-        <v>471.0500449089885</v>
+        <v>828.1598578775572</v>
       </c>
       <c r="E65">
-        <v>471.05</v>
+        <v>828.16</v>
       </c>
       <c r="F65">
-        <v>471.05</v>
+        <v>828.16</v>
       </c>
       <c r="G65">
-        <v>1043132.6328125</v>
+        <v>2267763.24325</v>
       </c>
       <c r="H65">
-        <v>754393.3399999993</v>
+        <v>1368111.3999999997</v>
       </c>
       <c r="I65">
-        <v>754134.0499999996</v>
+        <v>1369518.230000005</v>
       </c>
       <c r="J65">
-        <v>-288998.5828125004</v>
+        <v>-0.3960929413260499</v>
       </c>
       <c r="K65">
-        <v>-288739.29281250073</v>
+        <v>-0.3967133014999758</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6063,7 +6103,7 @@
         <v>8760</v>
       </c>
       <c r="N65">
-        <v>778.0</v>
+        <v>1361.0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6102,7 +6142,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B1091</t>
+          <t>B1095</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6111,28 +6151,28 @@
         </is>
       </c>
       <c r="D66">
-        <v>828.1598578775572</v>
+        <v>703.5313294888409</v>
       </c>
       <c r="E66">
-        <v>828.16</v>
+        <v>712.3</v>
       </c>
       <c r="F66">
-        <v>828.16</v>
+        <v>712.3</v>
       </c>
       <c r="G66">
-        <v>2256728.2558750003</v>
+        <v>1913829.6795</v>
       </c>
       <c r="H66">
-        <v>1265034.9400000004</v>
+        <v>1231509.7400000002</v>
       </c>
       <c r="I66">
-        <v>1263624.0500000047</v>
+        <v>1231365.3299999943</v>
       </c>
       <c r="J66">
-        <v>-993104.2058749956</v>
+        <v>-0.3565961782337412</v>
       </c>
       <c r="K66">
-        <v>-991693.3158749999</v>
+        <v>-0.35652072219836206</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6143,7 +6183,7 @@
         <v>8760</v>
       </c>
       <c r="N66">
-        <v>1367.0</v>
+        <v>1162.0</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6182,7 +6222,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B1095</t>
+          <t>B1097</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6191,28 +6231,28 @@
         </is>
       </c>
       <c r="D67">
-        <v>703.5313294888409</v>
+        <v>15.575723734124185</v>
       </c>
       <c r="E67">
-        <v>712.3</v>
+        <v>15.58</v>
       </c>
       <c r="F67">
-        <v>712.3</v>
+        <v>15.58</v>
       </c>
       <c r="G67">
-        <v>1909926.74325</v>
+        <v>34614.4205</v>
       </c>
       <c r="H67">
-        <v>1147119.5500000005</v>
+        <v>26637.46000000004</v>
       </c>
       <c r="I67">
-        <v>1147798.590000003</v>
+        <v>26712.810000000052</v>
       </c>
       <c r="J67">
-        <v>-762128.153249997</v>
+        <v>-0.22827510574674933</v>
       </c>
       <c r="K67">
-        <v>-762807.1932499995</v>
+        <v>-0.23045194415431455</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6223,7 +6263,7 @@
         <v>8760</v>
       </c>
       <c r="N67">
-        <v>1162.0</v>
+        <v>26.0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6262,7 +6302,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B1097</t>
+          <t>B1098</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6271,28 +6311,28 @@
         </is>
       </c>
       <c r="D68">
-        <v>15.575723734124185</v>
+        <v>10.045666343431867</v>
       </c>
       <c r="E68">
-        <v>15.58</v>
+        <v>10.05</v>
       </c>
       <c r="F68">
-        <v>15.58</v>
+        <v>10.05</v>
       </c>
       <c r="G68">
-        <v>36320.829625</v>
+        <v>20633.5035</v>
       </c>
       <c r="H68">
-        <v>24786.279999999988</v>
+        <v>17196.809999999998</v>
       </c>
       <c r="I68">
-        <v>24854.319999999985</v>
+        <v>17190.36999999997</v>
       </c>
       <c r="J68">
-        <v>-11466.509625000013</v>
+        <v>-0.16687100666157006</v>
       </c>
       <c r="K68">
-        <v>-11534.54962500001</v>
+        <v>-0.16655889291898496</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6303,7 +6343,7 @@
         <v>8760</v>
       </c>
       <c r="N68">
-        <v>26.0</v>
+        <v>15.0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6342,7 +6382,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B1098</t>
+          <t>B1099</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6351,28 +6391,28 @@
         </is>
       </c>
       <c r="D69">
-        <v>10.045666343431867</v>
+        <v>493.172912851294</v>
       </c>
       <c r="E69">
-        <v>10.05</v>
+        <v>493.17</v>
       </c>
       <c r="F69">
-        <v>10.05</v>
+        <v>493.17</v>
       </c>
       <c r="G69">
-        <v>20000.4769375</v>
+        <v>1060573.5794375</v>
       </c>
       <c r="H69">
-        <v>15970.450000000006</v>
+        <v>849689.4400000012</v>
       </c>
       <c r="I69">
-        <v>15998.78000000004</v>
+        <v>849748.2200000014</v>
       </c>
       <c r="J69">
-        <v>-4001.696937499959</v>
+        <v>-0.1987842838299959</v>
       </c>
       <c r="K69">
-        <v>-4030.0269374999934</v>
+        <v>-0.1988397066701833</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -6383,7 +6423,7 @@
         <v>8760</v>
       </c>
       <c r="N69">
-        <v>18.0</v>
+        <v>812.0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6422,7 +6462,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B1099</t>
+          <t>B1100</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6431,28 +6471,28 @@
         </is>
       </c>
       <c r="D70">
-        <v>493.172912851294</v>
+        <v>68.06694684477773</v>
       </c>
       <c r="E70">
-        <v>493.17</v>
+        <v>66.07</v>
       </c>
       <c r="F70">
-        <v>493.17</v>
+        <v>66.07</v>
       </c>
       <c r="G70">
-        <v>975541.649109375</v>
+        <v>129415.845</v>
       </c>
       <c r="H70">
-        <v>790722.8699999999</v>
+        <v>114440.9699999999</v>
       </c>
       <c r="I70">
-        <v>791022.4100000011</v>
+        <v>114410.4300000002</v>
       </c>
       <c r="J70">
-        <v>-184519.23910937388</v>
+        <v>-0.11594727832592527</v>
       </c>
       <c r="K70">
-        <v>-184818.7791093751</v>
+        <v>-0.11571129485728816</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -6463,7 +6503,7 @@
         <v>8760</v>
       </c>
       <c r="N70">
-        <v>813.0</v>
+        <v>111.0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6502,7 +6542,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B1100</t>
+          <t>B1101</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6511,28 +6551,28 @@
         </is>
       </c>
       <c r="D71">
-        <v>68.06694684477773</v>
+        <v>31.893622505005403</v>
       </c>
       <c r="E71">
-        <v>66.07</v>
+        <v>31.91</v>
       </c>
       <c r="F71">
-        <v>66.07</v>
+        <v>31.91</v>
       </c>
       <c r="G71">
-        <v>130285.482875</v>
+        <v>66440.65612500001</v>
       </c>
       <c r="H71">
-        <v>106667.09000000003</v>
+        <v>55365.099999999955</v>
       </c>
       <c r="I71">
-        <v>106705.20000000013</v>
+        <v>55411.01000000004</v>
       </c>
       <c r="J71">
-        <v>-23580.282874999873</v>
+        <v>-0.16600748349397745</v>
       </c>
       <c r="K71">
-        <v>-23618.392874999976</v>
+        <v>-0.16669847606806806</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6543,7 +6583,7 @@
         <v>8760</v>
       </c>
       <c r="N71">
-        <v>113.0</v>
+        <v>52.0</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6571,86 +6611,6 @@
         </is>
       </c>
       <c r="U71">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Alta_Lisboa</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>B1101</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>31.893622505005403</v>
-      </c>
-      <c r="E72">
-        <v>31.91</v>
-      </c>
-      <c r="F72">
-        <v>31.91</v>
-      </c>
-      <c r="G72">
-        <v>42033.007125000004</v>
-      </c>
-      <c r="H72">
-        <v>51677.90000000006</v>
-      </c>
-      <c r="I72">
-        <v>51684.94999999995</v>
-      </c>
-      <c r="J72">
-        <v>9651.94287499995</v>
-      </c>
-      <c r="K72">
-        <v>9644.892875000056</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>roofs_top_kW</t>
-        </is>
-      </c>
-      <c r="M72">
-        <v>8760</v>
-      </c>
-      <c r="N72">
-        <v>50.0</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>cea</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>MULTI_RES</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>roofs_top_kW</t>
-        </is>
-      </c>
-      <c r="U72">
         <v>8760</v>
       </c>
     </row>
@@ -6801,7 +6761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6906,13 +6866,13 @@
         <v>6850.44</v>
       </c>
       <c r="D2">
-        <v>10961652.96000001</v>
+        <v>11750669.109999998</v>
       </c>
       <c r="E2">
         <v>6850.44</v>
       </c>
       <c r="F2">
-        <v>10965002.000000032</v>
+        <v>11749716.379999992</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -6939,20 +6899,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B1002</t>
+          <t>B1001</t>
         </is>
       </c>
       <c r="C3">
-        <v>2906.82</v>
+        <v>1693.19</v>
       </c>
       <c r="D3">
-        <v>4702637.079999995</v>
+        <v>2936828.719999997</v>
       </c>
       <c r="E3">
-        <v>2906.82</v>
+        <v>1693.19</v>
       </c>
       <c r="F3">
-        <v>4704415.930000007</v>
+        <v>2937236.7100000083</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6979,20 +6939,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B1004</t>
+          <t>B1002</t>
         </is>
       </c>
       <c r="C4">
-        <v>3104.91</v>
+        <v>2906.82</v>
       </c>
       <c r="D4">
-        <v>5006093.889999985</v>
+        <v>5046186.889999997</v>
       </c>
       <c r="E4">
-        <v>3104.91</v>
+        <v>2906.82</v>
       </c>
       <c r="F4">
-        <v>5005239.359999985</v>
+        <v>5045631.119999985</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7019,20 +6979,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B1007</t>
+          <t>B1004</t>
         </is>
       </c>
       <c r="C5">
-        <v>930.44</v>
+        <v>3104.91</v>
       </c>
       <c r="D5">
-        <v>1477440.4099999936</v>
+        <v>5357884.150000015</v>
       </c>
       <c r="E5">
-        <v>930.44</v>
+        <v>3104.91</v>
       </c>
       <c r="F5">
-        <v>1477244.2899999975</v>
+        <v>5357553.279999997</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7059,20 +7019,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B1008</t>
+          <t>B1007</t>
         </is>
       </c>
       <c r="C6">
-        <v>873.88</v>
+        <v>930.44</v>
       </c>
       <c r="D6">
-        <v>1394230.5199999916</v>
+        <v>1590331.260000006</v>
       </c>
       <c r="E6">
-        <v>866.55</v>
+        <v>930.44</v>
       </c>
       <c r="F6">
-        <v>1377973.0300000003</v>
+        <v>1589563.1200000024</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7089,21 +7049,6 @@
       </c>
       <c r="L6">
         <v>8760</v>
-      </c>
-      <c r="M6">
-        <v>2.0</v>
-      </c>
-      <c r="N6">
-        <v>0.6519851982593536</v>
-      </c>
-      <c r="O6">
-        <v>0.6512348791154575</v>
-      </c>
-      <c r="P6">
-        <v>0.5486889481544495</v>
-      </c>
-      <c r="Q6">
-        <v>0.7552814483642578</v>
       </c>
     </row>
     <row r="7">
@@ -7114,20 +7059,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B1009</t>
+          <t>B1008</t>
         </is>
       </c>
       <c r="C7">
-        <v>876.17</v>
+        <v>872.5</v>
       </c>
       <c r="D7">
-        <v>1333652.9599999972</v>
+        <v>1474814.5499999996</v>
       </c>
       <c r="E7">
-        <v>872.61</v>
+        <v>866.55</v>
       </c>
       <c r="F7">
-        <v>1324113.2799999968</v>
+        <v>1479402.0700000008</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7149,16 +7094,16 @@
         <v>2.0</v>
       </c>
       <c r="N7">
-        <v>0.6965939402580261</v>
+        <v>0.6519851982593536</v>
       </c>
       <c r="O7">
-        <v>0.6963810102754568</v>
+        <v>0.6512579033929947</v>
       </c>
       <c r="P7">
-        <v>0.6317542791366577</v>
+        <v>0.5486889481544495</v>
       </c>
       <c r="Q7">
-        <v>0.7614336013793945</v>
+        <v>0.7552814483642578</v>
       </c>
     </row>
     <row r="8">
@@ -7169,20 +7114,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B1010</t>
+          <t>B1009</t>
         </is>
       </c>
       <c r="C8">
-        <v>2943.28</v>
+        <v>875.18</v>
       </c>
       <c r="D8">
-        <v>4762766.0</v>
+        <v>1427502.510000007</v>
       </c>
       <c r="E8">
-        <v>2943.28</v>
+        <v>872.61</v>
       </c>
       <c r="F8">
-        <v>4763740.4399999995</v>
+        <v>1431292.3500000006</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7199,6 +7144,21 @@
       </c>
       <c r="L8">
         <v>8760</v>
+      </c>
+      <c r="M8">
+        <v>2.0</v>
+      </c>
+      <c r="N8">
+        <v>0.6965939402580261</v>
+      </c>
+      <c r="O8">
+        <v>0.6964081099397869</v>
+      </c>
+      <c r="P8">
+        <v>0.6317542791366577</v>
+      </c>
+      <c r="Q8">
+        <v>0.7614336013793945</v>
       </c>
     </row>
     <row r="9">
@@ -7209,20 +7169,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B1011</t>
+          <t>B1010</t>
         </is>
       </c>
       <c r="C9">
-        <v>970.93</v>
+        <v>2943.28</v>
       </c>
       <c r="D9">
-        <v>1097475.6700000013</v>
+        <v>5109330.949999997</v>
       </c>
       <c r="E9">
-        <v>970.93</v>
+        <v>2943.28</v>
       </c>
       <c r="F9">
-        <v>1099064.0999999996</v>
+        <v>5109272.099999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7249,20 +7209,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B1012</t>
+          <t>B1011</t>
         </is>
       </c>
       <c r="C10">
-        <v>272.61</v>
+        <v>970.93</v>
       </c>
       <c r="D10">
-        <v>440376.8599999997</v>
+        <v>1190379.199999998</v>
       </c>
       <c r="E10">
-        <v>272.61</v>
+        <v>970.93</v>
       </c>
       <c r="F10">
-        <v>440195.63000000006</v>
+        <v>1186057.9000000013</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7289,20 +7249,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B1013</t>
+          <t>B1012</t>
         </is>
       </c>
       <c r="C11">
-        <v>118.42</v>
+        <v>272.61</v>
       </c>
       <c r="D11">
-        <v>200648.88999999998</v>
+        <v>472462.0000000018</v>
       </c>
       <c r="E11">
-        <v>110.34</v>
+        <v>272.61</v>
       </c>
       <c r="F11">
-        <v>170984.0799999996</v>
+        <v>472107.95000000065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -7319,21 +7279,6 @@
       </c>
       <c r="L11">
         <v>8760</v>
-      </c>
-      <c r="M11">
-        <v>2.0</v>
-      </c>
-      <c r="N11">
-        <v>0.6553257405757904</v>
-      </c>
-      <c r="O11">
-        <v>0.6553929188855259</v>
-      </c>
-      <c r="P11">
-        <v>0.5647161602973938</v>
-      </c>
-      <c r="Q11">
-        <v>0.745935320854187</v>
       </c>
     </row>
     <row r="12">
@@ -7344,20 +7289,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B1014</t>
+          <t>B1013</t>
         </is>
       </c>
       <c r="C12">
-        <v>220.9</v>
+        <v>114.65</v>
       </c>
       <c r="D12">
-        <v>336603.9000000002</v>
+        <v>202495.6600000001</v>
       </c>
       <c r="E12">
-        <v>214.57</v>
+        <v>110.34</v>
       </c>
       <c r="F12">
-        <v>344981.0700000008</v>
+        <v>176056.72999999992</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7376,19 +7321,19 @@
         <v>8760</v>
       </c>
       <c r="M12">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N12">
-        <v>0.8098851243654887</v>
+        <v>0.6553257405757904</v>
       </c>
       <c r="O12">
-        <v>0.7403211313604937</v>
+        <v>0.6530525516122397</v>
       </c>
       <c r="P12">
-        <v>0.5294176340103149</v>
+        <v>0.5647161602973938</v>
       </c>
       <c r="Q12">
-        <v>0.9927757978439331</v>
+        <v>0.745935320854187</v>
       </c>
     </row>
     <row r="13">
@@ -7399,20 +7344,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B1018</t>
+          <t>B1014</t>
         </is>
       </c>
       <c r="C13">
-        <v>2610.32</v>
+        <v>220.77</v>
       </c>
       <c r="D13">
-        <v>4069704.3199999994</v>
+        <v>358195.0000000003</v>
       </c>
       <c r="E13">
-        <v>2610.32</v>
+        <v>214.57</v>
       </c>
       <c r="F13">
-        <v>4075898.8800000018</v>
+        <v>368960.7099999988</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7429,6 +7374,21 @@
       </c>
       <c r="L13">
         <v>8760</v>
+      </c>
+      <c r="M13">
+        <v>3.0</v>
+      </c>
+      <c r="N13">
+        <v>0.8098851243654887</v>
+      </c>
+      <c r="O13">
+        <v>0.7402637658592744</v>
+      </c>
+      <c r="P13">
+        <v>0.5294176340103149</v>
+      </c>
+      <c r="Q13">
+        <v>0.9927757978439331</v>
       </c>
     </row>
     <row r="14">
@@ -7439,20 +7399,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B1019</t>
+          <t>B1018</t>
         </is>
       </c>
       <c r="C14">
-        <v>4092.56</v>
+        <v>2610.32</v>
       </c>
       <c r="D14">
-        <v>4266567.229999992</v>
+        <v>4398730.870000009</v>
       </c>
       <c r="E14">
-        <v>4092.56</v>
+        <v>2610.32</v>
       </c>
       <c r="F14">
-        <v>4281392.479999997</v>
+        <v>4400881.609999997</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7479,20 +7439,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B1021</t>
+          <t>B1019</t>
         </is>
       </c>
       <c r="C15">
-        <v>275.65</v>
+        <v>4092.56</v>
       </c>
       <c r="D15">
-        <v>424439.4299999992</v>
+        <v>4612887.960000006</v>
       </c>
       <c r="E15">
-        <v>275.65</v>
+        <v>4092.56</v>
       </c>
       <c r="F15">
-        <v>424043.3599999994</v>
+        <v>4623988.199999998</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7519,20 +7479,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B1023</t>
+          <t>B1021</t>
         </is>
       </c>
       <c r="C16">
-        <v>1505.95</v>
+        <v>275.65</v>
       </c>
       <c r="D16">
-        <v>2431548.340000005</v>
+        <v>454454.1599999994</v>
       </c>
       <c r="E16">
-        <v>1505.95</v>
+        <v>275.65</v>
       </c>
       <c r="F16">
-        <v>2430774.3600000055</v>
+        <v>453997.5499999992</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7559,20 +7519,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B1024</t>
+          <t>B1023</t>
         </is>
       </c>
       <c r="C17">
-        <v>170.72</v>
+        <v>1505.95</v>
       </c>
       <c r="D17">
-        <v>262125.30000000045</v>
+        <v>2609095.2300000046</v>
       </c>
       <c r="E17">
-        <v>167.51</v>
+        <v>1505.95</v>
       </c>
       <c r="F17">
-        <v>259209.0099999994</v>
+        <v>2608828.890000008</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7589,21 +7549,6 @@
       </c>
       <c r="L17">
         <v>8760</v>
-      </c>
-      <c r="M17">
-        <v>2.0</v>
-      </c>
-      <c r="N17">
-        <v>0.9814960360527039</v>
-      </c>
-      <c r="O17">
-        <v>0.9815283311860167</v>
-      </c>
-      <c r="P17">
-        <v>0.9661091566085815</v>
-      </c>
-      <c r="Q17">
-        <v>0.9968829154968262</v>
       </c>
     </row>
     <row r="18">
@@ -7614,20 +7559,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B1025</t>
+          <t>B1024</t>
         </is>
       </c>
       <c r="C18">
-        <v>809.61</v>
+        <v>170.25</v>
       </c>
       <c r="D18">
-        <v>1233442.319999997</v>
+        <v>282227.7499999999</v>
       </c>
       <c r="E18">
-        <v>793.68</v>
+        <v>167.51</v>
       </c>
       <c r="F18">
-        <v>1124284.56</v>
+        <v>279951.4500000005</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -7649,16 +7594,16 @@
         <v>2.0</v>
       </c>
       <c r="N18">
-        <v>0.5739879906177521</v>
+        <v>0.9814960360527039</v>
       </c>
       <c r="O18">
-        <v>0.5739654788123475</v>
+        <v>0.9815501190966867</v>
       </c>
       <c r="P18">
-        <v>0.5584376454353333</v>
+        <v>0.9661091566085815</v>
       </c>
       <c r="Q18">
-        <v>0.5895383358001709</v>
+        <v>0.9968829154968262</v>
       </c>
     </row>
     <row r="19">
@@ -7669,20 +7614,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B1027</t>
+          <t>B1025</t>
         </is>
       </c>
       <c r="C19">
-        <v>472.49</v>
+        <v>807.71</v>
       </c>
       <c r="D19">
-        <v>675050.3900000004</v>
+        <v>1309712.8800000087</v>
       </c>
       <c r="E19">
-        <v>459.9</v>
+        <v>793.68</v>
       </c>
       <c r="F19">
-        <v>692277.5800000004</v>
+        <v>1221695.8700000027</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7701,19 +7646,19 @@
         <v>8760</v>
       </c>
       <c r="M19">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N19">
-        <v>0.5485995511213938</v>
+        <v>0.5739879906177521</v>
       </c>
       <c r="O19">
-        <v>0.5732750894511763</v>
+        <v>0.573995562871005</v>
       </c>
       <c r="P19">
-        <v>0.49337705969810486</v>
+        <v>0.5584376454353333</v>
       </c>
       <c r="Q19">
-        <v>0.6473819017410278</v>
+        <v>0.5895383358001709</v>
       </c>
     </row>
     <row r="20">
@@ -7724,20 +7669,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B1028</t>
+          <t>B1027</t>
         </is>
       </c>
       <c r="C20">
-        <v>738.25</v>
+        <v>470.62</v>
       </c>
       <c r="D20">
-        <v>825270.9500000033</v>
+        <v>734897.1999999968</v>
       </c>
       <c r="E20">
-        <v>738.25</v>
+        <v>459.9</v>
       </c>
       <c r="F20">
-        <v>823350.8100000016</v>
+        <v>750244.2199999979</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7754,6 +7699,21 @@
       </c>
       <c r="L20">
         <v>8760</v>
+      </c>
+      <c r="M20">
+        <v>3.0</v>
+      </c>
+      <c r="N20">
+        <v>0.5485995511213938</v>
+      </c>
+      <c r="O20">
+        <v>0.573283185298977</v>
+      </c>
+      <c r="P20">
+        <v>0.49337705969810486</v>
+      </c>
+      <c r="Q20">
+        <v>0.6473819017410278</v>
       </c>
     </row>
     <row r="21">
@@ -7764,20 +7724,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B1029</t>
+          <t>B1028</t>
         </is>
       </c>
       <c r="C21">
-        <v>478.27</v>
+        <v>738.25</v>
       </c>
       <c r="D21">
-        <v>694464.6499999969</v>
+        <v>877633.200000001</v>
       </c>
       <c r="E21">
-        <v>476.33</v>
+        <v>738.25</v>
       </c>
       <c r="F21">
-        <v>694707.3200000023</v>
+        <v>901705.450000002</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -7794,21 +7754,6 @@
       </c>
       <c r="L21">
         <v>8760</v>
-      </c>
-      <c r="M21">
-        <v>1.0</v>
-      </c>
-      <c r="N21">
-        <v>0.4284673035144806</v>
-      </c>
-      <c r="O21">
-        <v>0.4284673035144806</v>
-      </c>
-      <c r="P21">
-        <v>0.4284673035144806</v>
-      </c>
-      <c r="Q21">
-        <v>0.4284673035144806</v>
       </c>
     </row>
     <row r="22">
@@ -7819,20 +7764,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B1030</t>
+          <t>B1029</t>
         </is>
       </c>
       <c r="C22">
-        <v>476.68</v>
+        <v>476.35</v>
       </c>
       <c r="D22">
-        <v>744576.990000001</v>
+        <v>750668.7899999996</v>
       </c>
       <c r="E22">
-        <v>467.82</v>
+        <v>476.33</v>
       </c>
       <c r="F22">
-        <v>753799.4000000014</v>
+        <v>752372.6999999979</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7851,19 +7796,19 @@
         <v>8760</v>
       </c>
       <c r="M22">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="N22">
-        <v>0.6775287389755249</v>
+        <v>0.4284673035144806</v>
       </c>
       <c r="O22">
-        <v>0.627718954474629</v>
+        <v>0.4284673035144806</v>
       </c>
       <c r="P22">
-        <v>0.46839380264282227</v>
+        <v>0.4284673035144806</v>
       </c>
       <c r="Q22">
-        <v>0.8744791150093079</v>
+        <v>0.4284673035144806</v>
       </c>
     </row>
     <row r="23">
@@ -7874,20 +7819,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B1032</t>
+          <t>B1030</t>
         </is>
       </c>
       <c r="C23">
-        <v>759.24</v>
+        <v>475.21</v>
       </c>
       <c r="D23">
-        <v>1228978.2199999988</v>
+        <v>801171.3399999978</v>
       </c>
       <c r="E23">
-        <v>759.24</v>
+        <v>467.82</v>
       </c>
       <c r="F23">
-        <v>1227931.3199999996</v>
+        <v>808915.1500000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7904,6 +7849,21 @@
       </c>
       <c r="L23">
         <v>8760</v>
+      </c>
+      <c r="M23">
+        <v>3.0</v>
+      </c>
+      <c r="N23">
+        <v>0.6775287389755249</v>
+      </c>
+      <c r="O23">
+        <v>0.6276030359295445</v>
+      </c>
+      <c r="P23">
+        <v>0.46839380264282227</v>
+      </c>
+      <c r="Q23">
+        <v>0.8744791150093079</v>
       </c>
     </row>
     <row r="24">
@@ -7914,20 +7874,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B1036</t>
+          <t>B1032</t>
         </is>
       </c>
       <c r="C24">
-        <v>2398.34</v>
+        <v>759.24</v>
       </c>
       <c r="D24">
-        <v>3881202.990000004</v>
+        <v>1317595.4699999967</v>
       </c>
       <c r="E24">
-        <v>2398.34</v>
+        <v>759.24</v>
       </c>
       <c r="F24">
-        <v>3881972.889999992</v>
+        <v>1316914.5099999984</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -7954,20 +7914,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B1058</t>
+          <t>B1036</t>
         </is>
       </c>
       <c r="C25">
-        <v>2320.8</v>
+        <v>2398.34</v>
       </c>
       <c r="D25">
-        <v>3312791.730000007</v>
+        <v>4161942.5100000016</v>
       </c>
       <c r="E25">
-        <v>2320.8</v>
+        <v>2398.34</v>
       </c>
       <c r="F25">
-        <v>3313842.670000004</v>
+        <v>4162731.5000000102</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7994,20 +7954,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B1059</t>
+          <t>B1058</t>
         </is>
       </c>
       <c r="C26">
-        <v>1297.8</v>
+        <v>2320.8</v>
       </c>
       <c r="D26">
-        <v>2062914.299999996</v>
+        <v>3507124.8299999936</v>
       </c>
       <c r="E26">
-        <v>1297.8</v>
+        <v>2320.8</v>
       </c>
       <c r="F26">
-        <v>2062874.939999997</v>
+        <v>3514969.899999995</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -8034,20 +7994,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B1060</t>
+          <t>B1059</t>
         </is>
       </c>
       <c r="C27">
-        <v>238.47</v>
+        <v>1297.8</v>
       </c>
       <c r="D27">
-        <v>372494.49000000005</v>
+        <v>2204445.7400000067</v>
       </c>
       <c r="E27">
-        <v>238.47</v>
+        <v>1297.8</v>
       </c>
       <c r="F27">
-        <v>372579.0499999998</v>
+        <v>2204028.2899999986</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8074,20 +8034,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B1090</t>
+          <t>B1060</t>
         </is>
       </c>
       <c r="C28">
-        <v>799.84</v>
+        <v>238.47</v>
       </c>
       <c r="D28">
-        <v>1284430.5000000005</v>
+        <v>402066.18999999965</v>
       </c>
       <c r="E28">
-        <v>799.84</v>
+        <v>238.47</v>
       </c>
       <c r="F28">
-        <v>1283924.8700000017</v>
+        <v>402468.99000000005</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8114,20 +8074,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B1092</t>
+          <t>B1090</t>
         </is>
       </c>
       <c r="C29">
-        <v>575.41</v>
+        <v>799.84</v>
       </c>
       <c r="D29">
-        <v>901686.1600000004</v>
+        <v>1379738.2499999984</v>
       </c>
       <c r="E29">
-        <v>575.41</v>
+        <v>799.84</v>
       </c>
       <c r="F29">
-        <v>901209.3799999985</v>
+        <v>1378389.9100000053</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8154,20 +8114,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B1093</t>
+          <t>B1092</t>
         </is>
       </c>
       <c r="C30">
-        <v>301.74</v>
+        <v>575.41</v>
       </c>
       <c r="D30">
-        <v>450223.06999999983</v>
+        <v>973503.4599999986</v>
       </c>
       <c r="E30">
-        <v>301.74</v>
+        <v>575.41</v>
       </c>
       <c r="F30">
-        <v>447112.52999999915</v>
+        <v>973429.3599999979</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -8194,20 +8154,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B1094</t>
+          <t>B1093</t>
         </is>
       </c>
       <c r="C31">
-        <v>451.42</v>
+        <v>301.74</v>
       </c>
       <c r="D31">
-        <v>703839.7899999997</v>
+        <v>489840.9200000032</v>
       </c>
       <c r="E31">
-        <v>451.42</v>
+        <v>301.74</v>
       </c>
       <c r="F31">
-        <v>703236.0199999971</v>
+        <v>487262.08000000083</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -8234,35 +8194,75 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>B1094</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>451.42</v>
+      </c>
+      <c r="D32">
+        <v>764302.9500000017</v>
+      </c>
+      <c r="E32">
+        <v>451.42</v>
+      </c>
+      <c r="F32">
+        <v>764168.6800000012</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>roofs_top_kW</t>
+        </is>
+      </c>
+      <c r="J32">
+        <v>8760</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>roofs_top_kW</t>
+        </is>
+      </c>
+      <c r="L32">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alta_Lisboa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>B1096</t>
         </is>
       </c>
-      <c r="C32">
+      <c r="C33">
         <v>1432.54</v>
       </c>
-      <c r="D32">
-        <v>2249154.079999993</v>
-      </c>
-      <c r="E32">
+      <c r="D33">
+        <v>2381664.61</v>
+      </c>
+      <c r="E33">
         <v>1432.54</v>
       </c>
-      <c r="F32">
-        <v>2249694.99</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>roofs_top_kW</t>
-        </is>
-      </c>
-      <c r="J32">
-        <v>8760</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>roofs_top_kW</t>
-        </is>
-      </c>
-      <c r="L32">
+      <c r="F33">
+        <v>2383809.0100000016</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>roofs_top_kW</t>
+        </is>
+      </c>
+      <c r="J33">
+        <v>8760</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>roofs_top_kW</t>
+        </is>
+      </c>
+      <c r="L33">
         <v>8760</v>
       </c>
     </row>

--- a/tools/comparison_outputs/Alta_Lisboa_radiation_comparison.xlsx
+++ b/tools/comparison_outputs/Alta_Lisboa_radiation_comparison.xlsx
@@ -195,7 +195,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>30364.06000000001</v>
+        <v>30344.070000000003</v>
       </c>
     </row>
     <row r="16">
@@ -225,7 +225,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>50947617.550000004</v>
+        <v>50621829.330000006</v>
       </c>
     </row>
     <row r="19">
@@ -235,7 +235,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>50909874.920000024</v>
+        <v>50542339.160000026</v>
       </c>
     </row>
     <row r="20">
@@ -245,7 +245,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>-26.728263196077652</v>
+        <v>-27.19680460895591</v>
       </c>
     </row>
     <row r="21">
@@ -255,7 +255,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>-26.782543811828376</v>
+        <v>-27.311125613446873</v>
       </c>
     </row>
   </sheetData>
@@ -419,7 +419,7 @@
         <v>316.63596337502787</v>
       </c>
       <c r="E2">
-        <v>319.51</v>
+        <v>320.23</v>
       </c>
       <c r="F2">
         <v>316.6</v>
@@ -428,16 +428,16 @@
         <v>722452.69621875</v>
       </c>
       <c r="H2">
-        <v>539961.5199999999</v>
+        <v>518469.0</v>
       </c>
       <c r="I2">
-        <v>514414.79999999935</v>
+        <v>506833.9000000004</v>
       </c>
       <c r="J2">
-        <v>-0.2879605783293516</v>
+        <v>-0.2984538605050244</v>
       </c>
       <c r="K2">
-        <v>-0.2525994811478895</v>
+        <v>-0.2823488614360243</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         <v>0.6940101385116577</v>
       </c>
       <c r="X2">
-        <v>0.634689014100703</v>
+        <v>0.633941413094328</v>
       </c>
       <c r="Y2">
         <v>0.4489450454711914</v>
@@ -523,16 +523,16 @@
         <v>6461016.0353125</v>
       </c>
       <c r="H3">
-        <v>5279354.109999982</v>
+        <v>5279842.170000022</v>
       </c>
       <c r="I3">
-        <v>5279952.880000014</v>
+        <v>5278975.140000027</v>
       </c>
       <c r="J3">
-        <v>-0.1827983631146276</v>
+        <v>-0.1829496922546024</v>
       </c>
       <c r="K3">
-        <v>-0.1828910373932178</v>
+        <v>-0.18281549819050213</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -603,16 +603,16 @@
         <v>2151885.359375</v>
       </c>
       <c r="H4">
-        <v>1633554.3200000057</v>
+        <v>1636518.369999998</v>
       </c>
       <c r="I4">
-        <v>1633098.3799999994</v>
+        <v>1637562.1700000037</v>
       </c>
       <c r="J4">
-        <v>-0.24108485943028052</v>
+        <v>-0.23901049706680375</v>
       </c>
       <c r="K4">
-        <v>-0.24087298011337369</v>
+        <v>-0.2394955600816424</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>183.52575815737313</v>
       </c>
       <c r="E5">
-        <v>180.52</v>
+        <v>186.33</v>
       </c>
       <c r="F5">
         <v>185.7</v>
@@ -683,16 +683,16 @@
         <v>382455.332625</v>
       </c>
       <c r="H5">
-        <v>307023.2399999995</v>
+        <v>316170.53999999934</v>
       </c>
       <c r="I5">
-        <v>320436.45</v>
+        <v>320501.34999999945</v>
       </c>
       <c r="J5">
-        <v>-0.1621598062166645</v>
+        <v>-0.1619901131977334</v>
       </c>
       <c r="K5">
-        <v>-0.19723111744126764</v>
+        <v>-0.17331381463569062</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>0.6830049157142639</v>
       </c>
       <c r="X5">
-        <v>0.6836608447089686</v>
+        <v>0.6834668882560337</v>
       </c>
       <c r="Y5">
         <v>0.6775040626525879</v>
@@ -778,16 +778,16 @@
         <v>1041488.901328125</v>
       </c>
       <c r="H6">
-        <v>880636.9800000046</v>
+        <v>880874.4600000061</v>
       </c>
       <c r="I6">
-        <v>880725.7300000016</v>
+        <v>881577.9700000011</v>
       </c>
       <c r="J6">
-        <v>-0.1543589865654021</v>
+        <v>-0.15354069652033991</v>
       </c>
       <c r="K6">
-        <v>-0.15444420110766344</v>
+        <v>-0.15421618139502066</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>365252.92209375004</v>
       </c>
       <c r="H7">
-        <v>295944.91999999963</v>
+        <v>295641.5800000002</v>
       </c>
       <c r="I7">
-        <v>295766.63999999897</v>
+        <v>295903.55000000034</v>
       </c>
       <c r="J7">
-        <v>-0.19024155014402847</v>
+        <v>-0.1898667139915439</v>
       </c>
       <c r="K7">
-        <v>-0.18975345001062308</v>
+        <v>-0.19058394302423293</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         <v>10438925.579078125</v>
       </c>
       <c r="H8">
-        <v>7525957.809999977</v>
+        <v>7527267.299999986</v>
       </c>
       <c r="I8">
-        <v>7524601.990000011</v>
+        <v>7528021.740000001</v>
       </c>
       <c r="J8">
-        <v>-0.2791785004118672</v>
+        <v>-0.2788509044371585</v>
       </c>
       <c r="K8">
-        <v>-0.2790486192292019</v>
+        <v>-0.2789231762427481</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1018,16 +1018,16 @@
         <v>1014674.485625</v>
       </c>
       <c r="H9">
-        <v>689365.6999999996</v>
+        <v>583640.0799999958</v>
       </c>
       <c r="I9">
-        <v>688799.9100000015</v>
+        <v>581515.3199999998</v>
       </c>
       <c r="J9">
-        <v>-0.3211616929780908</v>
+        <v>-0.4268947054071148</v>
       </c>
       <c r="K9">
-        <v>-0.3206040855798427</v>
+        <v>-0.4248006742374169</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1098,16 +1098,16 @@
         <v>3759624.0890078126</v>
       </c>
       <c r="H10">
-        <v>2789762.56999999</v>
+        <v>2790138.3700000043</v>
       </c>
       <c r="I10">
-        <v>2789624.430000003</v>
+        <v>2790202.2500000084</v>
       </c>
       <c r="J10">
-        <v>-0.2580044270499922</v>
+        <v>-0.2578507361526243</v>
       </c>
       <c r="K10">
-        <v>-0.2579676840148598</v>
+        <v>-0.25786772721303136</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1178,16 +1178,16 @@
         <v>1449804.290203125</v>
       </c>
       <c r="H11">
-        <v>1287157.4100000015</v>
+        <v>1286705.5500000021</v>
       </c>
       <c r="I11">
-        <v>1287503.8899999992</v>
+        <v>1286280.1700000032</v>
       </c>
       <c r="J11">
-        <v>-0.11194642014777503</v>
+        <v>-0.1127904788998874</v>
       </c>
       <c r="K11">
-        <v>-0.11218540412812254</v>
+        <v>-0.11249707378109074</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>378.38995699688985</v>
       </c>
       <c r="E12">
-        <v>378.38</v>
+        <v>378.39</v>
       </c>
       <c r="F12">
         <v>378.38</v>
@@ -1258,16 +1258,16 @@
         <v>951905.74384375</v>
       </c>
       <c r="H12">
-        <v>625601.8699999992</v>
+        <v>604449.2500000014</v>
       </c>
       <c r="I12">
-        <v>627903.4000000013</v>
+        <v>620533.6100000007</v>
       </c>
       <c r="J12">
-        <v>-0.34037229624799054</v>
+        <v>-0.3481144388368584</v>
       </c>
       <c r="K12">
-        <v>-0.3427901091615976</v>
+        <v>-0.3650114479199756</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>0.9890090823173523</v>
       </c>
       <c r="X12">
-        <v>0.9890090823173523</v>
+        <v>0.9890090823173522</v>
       </c>
       <c r="Y12">
         <v>0.9890090823173523</v>
@@ -1353,16 +1353,16 @@
         <v>1432575.848921875</v>
       </c>
       <c r="H13">
-        <v>1078085.9100000006</v>
+        <v>1076775.0300000021</v>
       </c>
       <c r="I13">
-        <v>1078304.2700000012</v>
+        <v>1076818.63</v>
       </c>
       <c r="J13">
-        <v>-0.24729690870364093</v>
+        <v>-0.2483339497797692</v>
       </c>
       <c r="K13">
-        <v>-0.24744933344273234</v>
+        <v>-0.24836438446846687</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>735.2452728248661</v>
       </c>
       <c r="E14">
-        <v>734.71</v>
+        <v>735.19</v>
       </c>
       <c r="F14">
         <v>732.46</v>
@@ -1433,16 +1433,16 @@
         <v>1445044.5366953125</v>
       </c>
       <c r="H14">
-        <v>1272632.4800000037</v>
+        <v>1269531.9600000018</v>
       </c>
       <c r="I14">
-        <v>1270517.9199999978</v>
+        <v>1271310.7799999965</v>
       </c>
       <c r="J14">
-        <v>-0.1207759430684686</v>
+        <v>-0.12022726793779623</v>
       </c>
       <c r="K14">
-        <v>-0.11931262484795085</v>
+        <v>-0.12145824729851733</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>0.9921562671661377</v>
       </c>
       <c r="X14">
-        <v>0.9921562671661377</v>
+        <v>0.9921562671661378</v>
       </c>
       <c r="Y14">
         <v>0.9921562671661377</v>
@@ -1528,16 +1528,16 @@
         <v>1096379.78125</v>
       </c>
       <c r="H15">
-        <v>743965.810000001</v>
+        <v>748999.5700000013</v>
       </c>
       <c r="I15">
-        <v>746862.0799999982</v>
+        <v>751955.3599999994</v>
       </c>
       <c r="J15">
-        <v>-0.3187925454549254</v>
+        <v>-0.31414700192420264</v>
       </c>
       <c r="K15">
-        <v>-0.32143421219260926</v>
+        <v>-0.3168429564196678</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>503.4881674734263</v>
       </c>
       <c r="E16">
-        <v>497.04</v>
+        <v>503.36</v>
       </c>
       <c r="F16">
         <v>491.6</v>
@@ -1608,16 +1608,16 @@
         <v>1165644.1205625</v>
       </c>
       <c r="H16">
-        <v>862701.0899999981</v>
+        <v>874399.0099999972</v>
       </c>
       <c r="I16">
-        <v>853288.3800000006</v>
+        <v>853052.6100000005</v>
       </c>
       <c r="J16">
-        <v>-0.26796835762511056</v>
+        <v>-0.2681706234761032</v>
       </c>
       <c r="K16">
-        <v>-0.2598932429018833</v>
+        <v>-0.24985765846093566</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1703,16 +1703,16 @@
         <v>1269227.792875</v>
       </c>
       <c r="H17">
-        <v>971308.1000000042</v>
+        <v>971190.2700000006</v>
       </c>
       <c r="I17">
-        <v>970665.6400000021</v>
+        <v>971713.6699999991</v>
       </c>
       <c r="J17">
-        <v>-0.2352313387329061</v>
+        <v>-0.23440561619052225</v>
       </c>
       <c r="K17">
-        <v>-0.23472515693984375</v>
+        <v>-0.23481799291512337</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1783,16 +1783,16 @@
         <v>934826.555390625</v>
       </c>
       <c r="H18">
-        <v>671672.1199999972</v>
+        <v>670144.4500000004</v>
       </c>
       <c r="I18">
-        <v>671548.7300000011</v>
+        <v>669498.8300000005</v>
       </c>
       <c r="J18">
-        <v>-0.2816328054358822</v>
+        <v>-0.2838256186247887</v>
       </c>
       <c r="K18">
-        <v>-0.2815008130365601</v>
+        <v>-0.28313498783742297</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1863,16 +1863,16 @@
         <v>516489.6829375</v>
       </c>
       <c r="H19">
-        <v>366093.43</v>
+        <v>397324.46000000014</v>
       </c>
       <c r="I19">
-        <v>365949.16999999905</v>
+        <v>397802.26999999984</v>
       </c>
       <c r="J19">
-        <v>-0.291468577031998</v>
+        <v>-0.22979628995195714</v>
       </c>
       <c r="K19">
-        <v>-0.2911892684518528</v>
+        <v>-0.23072140039614297</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1943,16 +1943,16 @@
         <v>1100404.8786875</v>
       </c>
       <c r="H20">
-        <v>784224.1900000022</v>
+        <v>772873.0300000012</v>
       </c>
       <c r="I20">
-        <v>784333.8800000036</v>
+        <v>774688.4900000008</v>
       </c>
       <c r="J20">
-        <v>-0.28723154977692195</v>
+        <v>-0.29599685987942465</v>
       </c>
       <c r="K20">
-        <v>-0.2873312312688218</v>
+        <v>-0.2976466708128013</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>370.47287369398555</v>
       </c>
       <c r="E21">
-        <v>377.68</v>
+        <v>378.92</v>
       </c>
       <c r="F21">
         <v>370.47</v>
@@ -2023,16 +2023,16 @@
         <v>806421.4786093751</v>
       </c>
       <c r="H21">
-        <v>582757.56</v>
+        <v>585609.9900000008</v>
       </c>
       <c r="I21">
-        <v>586335.2300000011</v>
+        <v>583783.6399999957</v>
       </c>
       <c r="J21">
-        <v>-0.27291714624082103</v>
+        <v>-0.2760812360718676</v>
       </c>
       <c r="K21">
-        <v>-0.2773536228165325</v>
+        <v>-0.2738164774457028</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>0.7904747724533081</v>
       </c>
       <c r="X21">
-        <v>0.801526068218561</v>
+        <v>0.8012858745341871</v>
       </c>
       <c r="Y21">
         <v>0.719028651714325</v>
@@ -2109,7 +2109,7 @@
         <v>236.53398952913864</v>
       </c>
       <c r="E22">
-        <v>240.14</v>
+        <v>240.08</v>
       </c>
       <c r="F22">
         <v>236.53</v>
@@ -2118,16 +2118,16 @@
         <v>559592.7028125001</v>
       </c>
       <c r="H22">
-        <v>367614.83000000066</v>
+        <v>367147.78999999986</v>
       </c>
       <c r="I22">
-        <v>366588.2300000012</v>
+        <v>365063.8899999982</v>
       </c>
       <c r="J22">
-        <v>-0.34490169697078393</v>
+        <v>-0.34762571390728386</v>
       </c>
       <c r="K22">
-        <v>-0.3430671483877882</v>
+        <v>-0.34390175541117046</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>0.8522438108921051</v>
       </c>
       <c r="X22">
-        <v>0.8521502356645682</v>
+        <v>0.8521497417596996</v>
       </c>
       <c r="Y22">
         <v>0.7339749336242676</v>
@@ -2204,7 +2204,7 @@
         <v>366.5435176578728</v>
       </c>
       <c r="E23">
-        <v>367.69</v>
+        <v>353.95</v>
       </c>
       <c r="F23">
         <v>366.54</v>
@@ -2213,16 +2213,16 @@
         <v>890316.30021875</v>
       </c>
       <c r="H23">
-        <v>539951.5100000006</v>
+        <v>552144.8299999984</v>
       </c>
       <c r="I23">
-        <v>550439.9700000006</v>
+        <v>559612.5899999994</v>
       </c>
       <c r="J23">
-        <v>-0.38174784639486226</v>
+        <v>-0.37144519328411374</v>
       </c>
       <c r="K23">
-        <v>-0.3935284461630828</v>
+        <v>-0.3798329539015102</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>0.6310444076855978</v>
       </c>
       <c r="X23">
-        <v>0.6109359084130974</v>
+        <v>0.6104917986502413</v>
       </c>
       <c r="Y23">
         <v>0.4843061566352844</v>
@@ -2299,7 +2299,7 @@
         <v>234.33676148704424</v>
       </c>
       <c r="E24">
-        <v>237.49</v>
+        <v>237.42</v>
       </c>
       <c r="F24">
         <v>234.34</v>
@@ -2308,16 +2308,16 @@
         <v>533411.51046875</v>
       </c>
       <c r="H24">
-        <v>360033.9999999998</v>
+        <v>341837.6299999988</v>
       </c>
       <c r="I24">
-        <v>365907.7299999989</v>
+        <v>360824.8199999993</v>
       </c>
       <c r="J24">
-        <v>-0.31402355813722993</v>
+        <v>-0.32355261759740694</v>
       </c>
       <c r="K24">
-        <v>-0.3250351877791125</v>
+        <v>-0.3591483811446072</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>0.9972227513790131</v>
       </c>
       <c r="X24">
-        <v>0.997224778035883</v>
+        <v>0.9972245177071134</v>
       </c>
       <c r="Y24">
         <v>0.9952940344810486</v>
@@ -2394,7 +2394,7 @@
         <v>369.2005635828266</v>
       </c>
       <c r="E25">
-        <v>367.51</v>
+        <v>365.93</v>
       </c>
       <c r="F25">
         <v>369.2</v>
@@ -2403,16 +2403,16 @@
         <v>895263.256078125</v>
       </c>
       <c r="H25">
-        <v>543706.2000000003</v>
+        <v>599196.269999998</v>
       </c>
       <c r="I25">
-        <v>582552.090000001</v>
+        <v>579893.3600000005</v>
       </c>
       <c r="J25">
-        <v>-0.3492952089288419</v>
+        <v>-0.35226498344147816</v>
       </c>
       <c r="K25">
-        <v>-0.3926856750696871</v>
+        <v>-0.33070382825171</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>0.7484132647514343</v>
       </c>
       <c r="X25">
-        <v>0.6981701350214314</v>
+        <v>0.6982920345600719</v>
       </c>
       <c r="Y25">
         <v>0.6164996027946472</v>
@@ -2489,7 +2489,7 @@
         <v>239.06366887064294</v>
       </c>
       <c r="E26">
-        <v>244.91</v>
+        <v>244.86</v>
       </c>
       <c r="F26">
         <v>239.06</v>
@@ -2498,16 +2498,16 @@
         <v>588706.8608437501</v>
       </c>
       <c r="H26">
-        <v>395414.7900000012</v>
+        <v>383320.7799999999</v>
       </c>
       <c r="I26">
-        <v>393658.0000000021</v>
+        <v>385178.6000000005</v>
       </c>
       <c r="J26">
-        <v>-0.331317458342848</v>
+        <v>-0.3457208916370493</v>
       </c>
       <c r="K26">
-        <v>-0.3283333076273608</v>
+        <v>-0.3488766557763323</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>0.9933198392391205</v>
       </c>
       <c r="X26">
-        <v>0.9933143407200014</v>
+        <v>0.9933159852928636</v>
       </c>
       <c r="Y26">
         <v>0.9876328706741333</v>
@@ -2584,7 +2584,7 @@
         <v>371.1067151006221</v>
       </c>
       <c r="E27">
-        <v>374.3</v>
+        <v>375.56</v>
       </c>
       <c r="F27">
         <v>371.11</v>
@@ -2593,16 +2593,16 @@
         <v>850291.7773125</v>
       </c>
       <c r="H27">
-        <v>619176.9500000001</v>
+        <v>622913.0799999997</v>
       </c>
       <c r="I27">
-        <v>609268.8900000011</v>
+        <v>610245.8899999986</v>
       </c>
       <c r="J27">
-        <v>-0.2834590357609892</v>
+        <v>-0.282310018416513</v>
       </c>
       <c r="K27">
-        <v>-0.27180649452236255</v>
+        <v>-0.2674125557595906</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>0.813204437494278</v>
       </c>
       <c r="X27">
-        <v>0.8330670060034264</v>
+        <v>0.8325922973661882</v>
       </c>
       <c r="Y27">
         <v>0.6857811808586121</v>
@@ -2679,7 +2679,7 @@
         <v>370.7444376004047</v>
       </c>
       <c r="E28">
-        <v>371.19</v>
+        <v>361.5</v>
       </c>
       <c r="F28">
         <v>370.74</v>
@@ -2688,16 +2688,16 @@
         <v>893793.9065</v>
       </c>
       <c r="H28">
-        <v>593374.3999999996</v>
+        <v>615661.1600000015</v>
       </c>
       <c r="I28">
-        <v>594756.2800000008</v>
+        <v>594120.3699999994</v>
       </c>
       <c r="J28">
-        <v>-0.3345711179336611</v>
+        <v>-0.33528259067405114</v>
       </c>
       <c r="K28">
-        <v>-0.33611720142108675</v>
+        <v>-0.31118219141718717</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>0.7062302728494009</v>
       </c>
       <c r="X28">
-        <v>0.7655380594806622</v>
+        <v>0.7662099909840393</v>
       </c>
       <c r="Y28">
         <v>0.4379631578922272</v>
@@ -2774,7 +2774,7 @@
         <v>237.23200376810422</v>
       </c>
       <c r="E29">
-        <v>242.52</v>
+        <v>242.29</v>
       </c>
       <c r="F29">
         <v>237.23</v>
@@ -2783,16 +2783,16 @@
         <v>584574.7331875</v>
       </c>
       <c r="H29">
-        <v>406187.7499999999</v>
+        <v>390146.7200000012</v>
       </c>
       <c r="I29">
-        <v>356633.54000000097</v>
+        <v>368737.5500000007</v>
       </c>
       <c r="J29">
-        <v>-0.38992652307192316</v>
+        <v>-0.3692208556647802</v>
       </c>
       <c r="K29">
-        <v>-0.30515684832085144</v>
+        <v>-0.332597360353474</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>0.8294468224048615</v>
       </c>
       <c r="X29">
-        <v>0.8296518009049669</v>
+        <v>0.8297632859597448</v>
       </c>
       <c r="Y29">
         <v>0.7087990045547485</v>
@@ -2869,7 +2869,7 @@
         <v>372.25901245316396</v>
       </c>
       <c r="E30">
-        <v>376.79</v>
+        <v>377.37</v>
       </c>
       <c r="F30">
         <v>372.26</v>
@@ -2878,16 +2878,16 @@
         <v>897705.558875</v>
       </c>
       <c r="H30">
-        <v>597127.5499999996</v>
+        <v>585491.27</v>
       </c>
       <c r="I30">
-        <v>588688.6000000001</v>
+        <v>588211.7799999994</v>
       </c>
       <c r="J30">
-        <v>-0.3442297486296714</v>
+        <v>-0.34476090274282867</v>
       </c>
       <c r="K30">
-        <v>-0.3348291718853599</v>
+        <v>-0.3477914175626419</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>0.9016911089420319</v>
       </c>
       <c r="X30">
-        <v>0.9064905634024182</v>
+        <v>0.9064373687873619</v>
       </c>
       <c r="Y30">
         <v>0.8705822825431824</v>
@@ -2964,7 +2964,7 @@
         <v>235.89975493456654</v>
       </c>
       <c r="E31">
-        <v>239.93</v>
+        <v>239.82</v>
       </c>
       <c r="F31">
         <v>235.9</v>
@@ -2973,16 +2973,16 @@
         <v>572696.5886875</v>
       </c>
       <c r="H31">
-        <v>403176.09999999974</v>
+        <v>399103.7399999988</v>
       </c>
       <c r="I31">
-        <v>402532.75999999995</v>
+        <v>403003.79000000004</v>
       </c>
       <c r="J31">
-        <v>-0.29712736560467334</v>
+        <v>-0.2963048882068603</v>
       </c>
       <c r="K31">
-        <v>-0.2960040133572395</v>
+        <v>-0.3031148641645298</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>0.9866441488265991</v>
       </c>
       <c r="X31">
-        <v>0.9866730437575632</v>
+        <v>0.9866718508720423</v>
       </c>
       <c r="Y31">
         <v>0.9758704900741577</v>
@@ -3059,7 +3059,7 @@
         <v>372.87641404951376</v>
       </c>
       <c r="E32">
-        <v>379.27</v>
+        <v>379.2</v>
       </c>
       <c r="F32">
         <v>372.88</v>
@@ -3068,16 +3068,16 @@
         <v>858762.7599375</v>
       </c>
       <c r="H32">
-        <v>581726.9200000005</v>
+        <v>580241.9800000004</v>
       </c>
       <c r="I32">
-        <v>634476.1899999996</v>
+        <v>631138.9999999993</v>
       </c>
       <c r="J32">
-        <v>-0.26117407554307986</v>
+        <v>-0.26506011969367066</v>
       </c>
       <c r="K32">
-        <v>-0.3225988047707867</v>
+        <v>-0.32432796685055376</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>238.60140604129373</v>
       </c>
       <c r="E33">
-        <v>243.47</v>
+        <v>243.5</v>
       </c>
       <c r="F33">
         <v>238.6</v>
@@ -3163,16 +3163,16 @@
         <v>586904.6228125</v>
       </c>
       <c r="H33">
-        <v>397755.0000000008</v>
+        <v>399727.50000000006</v>
       </c>
       <c r="I33">
-        <v>400110.34000000067</v>
+        <v>400855.539999999</v>
       </c>
       <c r="J33">
-        <v>-0.3182702530393512</v>
+        <v>-0.31700054077089557</v>
       </c>
       <c r="K33">
-        <v>-0.322283409365694</v>
+        <v>-0.3189225566422194</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>0.9899944961071014</v>
       </c>
       <c r="X33">
-        <v>0.9899965978240969</v>
+        <v>0.9899969336948173</v>
       </c>
       <c r="Y33">
         <v>0.9830652475357056</v>
@@ -3249,7 +3249,7 @@
         <v>369.61348279181516</v>
       </c>
       <c r="E34">
-        <v>379.78</v>
+        <v>379.34</v>
       </c>
       <c r="F34">
         <v>369.61</v>
@@ -3258,16 +3258,16 @@
         <v>898239.93771875</v>
       </c>
       <c r="H34">
-        <v>630150.38</v>
+        <v>633009.3300000009</v>
       </c>
       <c r="I34">
-        <v>625517.9499999981</v>
+        <v>625139.3299999986</v>
       </c>
       <c r="J34">
-        <v>-0.30361819405556706</v>
+        <v>-0.30403970726612534</v>
       </c>
       <c r="K34">
-        <v>-0.29846096400435507</v>
+        <v>-0.2952781284612576</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>0.7704202234745026</v>
       </c>
       <c r="X34">
-        <v>0.7741709593541907</v>
+        <v>0.7741062814860232</v>
       </c>
       <c r="Y34">
         <v>0.5520116090774536</v>
@@ -3353,16 +3353,16 @@
         <v>5424386.1137500005</v>
       </c>
       <c r="H35">
-        <v>3411092.7000000007</v>
+        <v>3200045.879999998</v>
       </c>
       <c r="I35">
-        <v>3412434.8700000052</v>
+        <v>3201373.469999997</v>
       </c>
       <c r="J35">
-        <v>-0.3709085602608565</v>
+        <v>-0.4098182904264506</v>
       </c>
       <c r="K35">
-        <v>-0.3711559928683183</v>
+        <v>-0.4100630351721526</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>124.26560305683645</v>
       </c>
       <c r="E36">
-        <v>126.24</v>
+        <v>126.23</v>
       </c>
       <c r="F36">
         <v>124.23</v>
@@ -3433,16 +3433,16 @@
         <v>264982.38575</v>
       </c>
       <c r="H36">
-        <v>225453.62999999936</v>
+        <v>225095.98000000042</v>
       </c>
       <c r="I36">
-        <v>210540.3000000003</v>
+        <v>209885.7900000009</v>
       </c>
       <c r="J36">
-        <v>-0.20545548941265696</v>
+        <v>-0.20792550264824197</v>
       </c>
       <c r="K36">
-        <v>-0.1491750315332069</v>
+        <v>-0.15052474388856465</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>123.18186977450087</v>
       </c>
       <c r="E37">
-        <v>125.03</v>
+        <v>118.92</v>
       </c>
       <c r="F37">
         <v>123.17</v>
@@ -3528,16 +3528,16 @@
         <v>277058.5811875</v>
       </c>
       <c r="H37">
-        <v>181634.44999999987</v>
+        <v>187695.16000000018</v>
       </c>
       <c r="I37">
-        <v>185055.21000000034</v>
+        <v>186577.86000000045</v>
       </c>
       <c r="J37">
-        <v>-0.33207190621262933</v>
+        <v>-0.32657613707429806</v>
       </c>
       <c r="K37">
-        <v>-0.34441860915660155</v>
+        <v>-0.32254341592481817</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>0.7779085437456766</v>
       </c>
       <c r="X37">
-        <v>0.7575092045177529</v>
+        <v>0.7563747943315283</v>
       </c>
       <c r="Y37">
         <v>0.6722833514213562</v>
@@ -3623,16 +3623,16 @@
         <v>279505.0353125</v>
       </c>
       <c r="H38">
-        <v>206213.97000000012</v>
+        <v>194853.31999999986</v>
       </c>
       <c r="I38">
-        <v>208929.51000000114</v>
+        <v>204550.3600000006</v>
       </c>
       <c r="J38">
-        <v>-0.25250180281579565</v>
+        <v>-0.2681693202009635</v>
       </c>
       <c r="K38">
-        <v>-0.26221733440528894</v>
+        <v>-0.3028629348943767</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>0.6666513085365295</v>
       </c>
       <c r="X38">
-        <v>0.6666460422440421</v>
+        <v>0.6666481890444158</v>
       </c>
       <c r="Y38">
         <v>0.6264314651489258</v>
@@ -3718,16 +3718,16 @@
         <v>247551.24514062502</v>
       </c>
       <c r="H39">
-        <v>210503.4900000006</v>
+        <v>205361.2900000006</v>
       </c>
       <c r="I39">
-        <v>210232.2200000003</v>
+        <v>205060.4400000001</v>
       </c>
       <c r="J39">
-        <v>-0.15075272644831628</v>
+        <v>-0.17164448159607285</v>
       </c>
       <c r="K39">
-        <v>-0.1496569129336389</v>
+        <v>-0.17042917767049737</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>121.72871093484056</v>
       </c>
       <c r="E40">
-        <v>126.23</v>
+        <v>126.3</v>
       </c>
       <c r="F40">
         <v>121.73</v>
@@ -3798,16 +3798,16 @@
         <v>235608.508375</v>
       </c>
       <c r="H40">
-        <v>187501.68000000023</v>
+        <v>183193.42000000013</v>
       </c>
       <c r="I40">
-        <v>175662.0400000003</v>
+        <v>180226.14000000025</v>
       </c>
       <c r="J40">
-        <v>-0.25443252787623233</v>
+        <v>-0.23506098636663786</v>
       </c>
       <c r="K40">
-        <v>-0.2041812017180289</v>
+        <v>-0.2224668741231314</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>0.9834159016609192</v>
       </c>
       <c r="X40">
-        <v>0.9834990528412552</v>
+        <v>0.9834923695480506</v>
       </c>
       <c r="Y40">
         <v>0.967885434627533</v>
@@ -3884,7 +3884,7 @@
         <v>120.87717554136132</v>
       </c>
       <c r="E41">
-        <v>123.74</v>
+        <v>123.73</v>
       </c>
       <c r="F41">
         <v>120.88</v>
@@ -3893,16 +3893,16 @@
         <v>269707.395125</v>
       </c>
       <c r="H41">
-        <v>204377.80999999947</v>
+        <v>201729.69000000035</v>
       </c>
       <c r="I41">
-        <v>198508.96000000017</v>
+        <v>195452.50999999986</v>
       </c>
       <c r="J41">
-        <v>-0.2639839930677534</v>
+        <v>-0.27531645949339123</v>
       </c>
       <c r="K41">
-        <v>-0.2422239297321548</v>
+        <v>-0.2520424220978232</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>0.9046740233898163</v>
       </c>
       <c r="X41">
-        <v>0.9050082442125046</v>
+        <v>0.9050305003761419</v>
       </c>
       <c r="Y41">
         <v>0.8122680187225342</v>
@@ -3979,7 +3979,7 @@
         <v>120.0414937883839</v>
       </c>
       <c r="E42">
-        <v>122.3</v>
+        <v>122.33</v>
       </c>
       <c r="F42">
         <v>120.04</v>
@@ -3988,16 +3988,16 @@
         <v>270018.56453125</v>
       </c>
       <c r="H42">
-        <v>205338.3100000007</v>
+        <v>205258.13999999987</v>
       </c>
       <c r="I42">
-        <v>204199.00000000052</v>
+        <v>201231.05999999953</v>
       </c>
       <c r="J42">
-        <v>-0.24375940463764662</v>
+        <v>-0.2547510192518244</v>
       </c>
       <c r="K42">
-        <v>-0.2395400280848603</v>
+        <v>-0.23983693359630173</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>0.8856760263442993</v>
       </c>
       <c r="X42">
-        <v>0.8858963498418937</v>
+        <v>0.885886133832419</v>
       </c>
       <c r="Y42">
         <v>0.778390109539032</v>
@@ -4083,16 +4083,16 @@
         <v>276318.81809375</v>
       </c>
       <c r="H43">
-        <v>206467.07000000007</v>
+        <v>206609.0600000001</v>
       </c>
       <c r="I43">
-        <v>205750.07000000015</v>
+        <v>196982.4899999998</v>
       </c>
       <c r="J43">
-        <v>-0.25538886052200443</v>
+        <v>-0.2871188022628007</v>
       </c>
       <c r="K43">
-        <v>-0.2527940318203391</v>
+        <v>-0.25228016888121824</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>0.9297216236591339</v>
       </c>
       <c r="X43">
-        <v>0.9297205351581003</v>
+        <v>0.9297251337711753</v>
       </c>
       <c r="Y43">
         <v>0.921430230140686</v>
@@ -4169,7 +4169,7 @@
         <v>125.47070361249024</v>
       </c>
       <c r="E44">
-        <v>127.4</v>
+        <v>127.39</v>
       </c>
       <c r="F44">
         <v>125.48</v>
@@ -4178,16 +4178,16 @@
         <v>275909.47353125</v>
       </c>
       <c r="H44">
-        <v>216238.72000000006</v>
+        <v>216368.73999999883</v>
       </c>
       <c r="I44">
-        <v>215600.3699999995</v>
+        <v>212705.16999999955</v>
       </c>
       <c r="J44">
-        <v>-0.21858293866962783</v>
+        <v>-0.22907623548523007</v>
       </c>
       <c r="K44">
-        <v>-0.21626931749587622</v>
+        <v>-0.21579807597475448</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.851101279258728</v>
       </c>
       <c r="X44">
-        <v>0.8510582489557049</v>
+        <v>0.8510361973543399</v>
       </c>
       <c r="Y44">
         <v>0.7123515605926514</v>
@@ -4264,7 +4264,7 @@
         <v>116.75256223313664</v>
       </c>
       <c r="E45">
-        <v>118.57</v>
+        <v>118.52</v>
       </c>
       <c r="F45">
         <v>116.75</v>
@@ -4273,16 +4273,16 @@
         <v>279143.835625</v>
       </c>
       <c r="H45">
-        <v>201668.6000000004</v>
+        <v>201636.1499999996</v>
       </c>
       <c r="I45">
-        <v>199929.34999999977</v>
+        <v>191503.72000000023</v>
       </c>
       <c r="J45">
-        <v>-0.28377658939750494</v>
+        <v>-0.313960419110723</v>
       </c>
       <c r="K45">
-        <v>-0.2775459305828244</v>
+        <v>-0.2776621788959142</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>0.8419512808322906</v>
       </c>
       <c r="X45">
-        <v>0.8418828661570861</v>
+        <v>0.8419988040296486</v>
       </c>
       <c r="Y45">
         <v>0.7161607146263123</v>
@@ -4359,7 +4359,7 @@
         <v>124.10312756987287</v>
       </c>
       <c r="E46">
-        <v>125.9</v>
+        <v>126.07</v>
       </c>
       <c r="F46">
         <v>124.1</v>
@@ -4368,16 +4368,16 @@
         <v>291034.884875</v>
       </c>
       <c r="H46">
-        <v>214372.36999999982</v>
+        <v>214090.04999999984</v>
       </c>
       <c r="I46">
-        <v>214446.27999999915</v>
+        <v>204540.21000000063</v>
       </c>
       <c r="J46">
-        <v>-0.26315953466504804</v>
+        <v>-0.29719693194906505</v>
       </c>
       <c r="K46">
-        <v>-0.26341349047529766</v>
+        <v>-0.2643835460070297</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>0.7650662958621979</v>
       </c>
       <c r="X46">
-        <v>0.7650008274414574</v>
+        <v>0.7650227528826635</v>
       </c>
       <c r="Y46">
         <v>0.6473265886306763</v>
@@ -4454,7 +4454,7 @@
         <v>130.9085264508188</v>
       </c>
       <c r="E47">
-        <v>132.72</v>
+        <v>132.74</v>
       </c>
       <c r="F47">
         <v>130.92</v>
@@ -4463,16 +4463,16 @@
         <v>292941.29778125003</v>
       </c>
       <c r="H47">
-        <v>224439.10000000018</v>
+        <v>224158.8599999998</v>
       </c>
       <c r="I47">
-        <v>223754.9800000001</v>
+        <v>222105.34000000014</v>
       </c>
       <c r="J47">
-        <v>-0.23617809542481746</v>
+        <v>-0.2418093942976442</v>
       </c>
       <c r="K47">
-        <v>-0.23384274699432425</v>
+        <v>-0.23479938916844897</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>0.8466036021709442</v>
       </c>
       <c r="X47">
-        <v>0.8466980929066061</v>
+        <v>0.8467186372341261</v>
       </c>
       <c r="Y47">
         <v>0.7241121530532837</v>
@@ -4549,7 +4549,7 @@
         <v>118.41081365152584</v>
       </c>
       <c r="E48">
-        <v>121.09</v>
+        <v>121.1</v>
       </c>
       <c r="F48">
         <v>118.44</v>
@@ -4558,16 +4558,16 @@
         <v>281187.1920625</v>
       </c>
       <c r="H48">
-        <v>205150.85999999952</v>
+        <v>204871.91999999934</v>
       </c>
       <c r="I48">
-        <v>200779.8799999999</v>
+        <v>194845.4799999999</v>
       </c>
       <c r="J48">
-        <v>-0.285956524095976</v>
+        <v>-0.3070613260482674</v>
       </c>
       <c r="K48">
-        <v>-0.2704117904687484</v>
+        <v>-0.27140379866782094</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>0.8725321888923645</v>
       </c>
       <c r="X48">
-        <v>0.8730019373729163</v>
+        <v>0.8729970640357773</v>
       </c>
       <c r="Y48">
         <v>0.762785792350769</v>
@@ -4644,7 +4644,7 @@
         <v>112.27774131099156</v>
       </c>
       <c r="E49">
-        <v>113.83</v>
+        <v>113.84</v>
       </c>
       <c r="F49">
         <v>112.23</v>
@@ -4653,16 +4653,16 @@
         <v>215944.514375</v>
       </c>
       <c r="H49">
-        <v>176188.7200000002</v>
+        <v>176128.15000000055</v>
       </c>
       <c r="I49">
-        <v>193890.17000000048</v>
+        <v>193873.80000000002</v>
       </c>
       <c r="J49">
-        <v>-0.10212968103788407</v>
+        <v>-0.10220548754793986</v>
       </c>
       <c r="K49">
-        <v>-0.18410189529501816</v>
+        <v>-0.18438238401303428</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4748,16 +4748,16 @@
         <v>135464.283875</v>
       </c>
       <c r="H50">
-        <v>98060.66000000016</v>
+        <v>98216.92000000023</v>
       </c>
       <c r="I50">
-        <v>98379.99999999993</v>
+        <v>98310.66000000006</v>
       </c>
       <c r="J50">
-        <v>-0.2737569107826214</v>
+        <v>-0.2742687800223676</v>
       </c>
       <c r="K50">
-        <v>-0.2761142849248302</v>
+        <v>-0.27496077054059403</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>110.62788457108744</v>
       </c>
       <c r="E51">
-        <v>112.3</v>
+        <v>112.31</v>
       </c>
       <c r="F51">
         <v>110.6</v>
@@ -4828,16 +4828,16 @@
         <v>253369.3274375</v>
       </c>
       <c r="H51">
-        <v>191601.66000000056</v>
+        <v>191814.4800000007</v>
       </c>
       <c r="I51">
-        <v>191129.89000000016</v>
+        <v>191308.27999999974</v>
       </c>
       <c r="J51">
-        <v>-0.24564708785775494</v>
+        <v>-0.2449430168409363</v>
       </c>
       <c r="K51">
-        <v>-0.24378510241235105</v>
+        <v>-0.24294514280811425</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>0.9626638889312744</v>
       </c>
       <c r="X51">
-        <v>0.9626838051242314</v>
+        <v>0.9626904525182852</v>
       </c>
       <c r="Y51">
         <v>0.9442288279533386</v>
@@ -4914,7 +4914,7 @@
         <v>58.5967501938149</v>
       </c>
       <c r="E52">
-        <v>61.21</v>
+        <v>59.74</v>
       </c>
       <c r="F52">
         <v>58.6</v>
@@ -4923,16 +4923,16 @@
         <v>119194.47425</v>
       </c>
       <c r="H52">
-        <v>106030.69000000006</v>
+        <v>103521.44999999987</v>
       </c>
       <c r="I52">
-        <v>100388.20999999973</v>
+        <v>100198.83000000006</v>
       </c>
       <c r="J52">
-        <v>-0.1577779873465927</v>
+        <v>-0.15936681938928002</v>
       </c>
       <c r="K52">
-        <v>-0.11043955126971784</v>
+        <v>-0.13149119830108344</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>0.9952588081359863</v>
       </c>
       <c r="X52">
-        <v>0.9945255588123589</v>
+        <v>0.9944092583263212</v>
       </c>
       <c r="Y52">
         <v>0.991319477558136</v>
@@ -5009,7 +5009,7 @@
         <v>119.07112961905189</v>
       </c>
       <c r="E53">
-        <v>122.2</v>
+        <v>122.07</v>
       </c>
       <c r="F53">
         <v>119.05</v>
@@ -5018,16 +5018,16 @@
         <v>267140.7060625</v>
       </c>
       <c r="H53">
-        <v>206125.56000000035</v>
+        <v>205241.84999999934</v>
       </c>
       <c r="I53">
-        <v>205752.11000000034</v>
+        <v>201652.92000000027</v>
       </c>
       <c r="J53">
-        <v>-0.22979873403545342</v>
+        <v>-0.24514341909083026</v>
       </c>
       <c r="K53">
-        <v>-0.22840078160242872</v>
+        <v>-0.23170881358687012</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>0.843268871307373</v>
       </c>
       <c r="X53">
-        <v>0.8438735427448264</v>
+        <v>0.8439802614170354</v>
       </c>
       <c r="Y53">
         <v>0.6907517313957214</v>
@@ -5104,7 +5104,7 @@
         <v>168.56033444445646</v>
       </c>
       <c r="E54">
-        <v>175.18</v>
+        <v>173.03</v>
       </c>
       <c r="F54">
         <v>150.52</v>
@@ -5113,16 +5113,16 @@
         <v>361110.8783125</v>
       </c>
       <c r="H54">
-        <v>298728.4899999997</v>
+        <v>293516.919999999</v>
       </c>
       <c r="I54">
-        <v>260199.59999999995</v>
+        <v>260009.5299999995</v>
       </c>
       <c r="J54">
-        <v>-0.27944679701721126</v>
+        <v>-0.2799731450488426</v>
       </c>
       <c r="K54">
-        <v>-0.17275134054121605</v>
+        <v>-0.18718338984517163</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>0.9855310320854187</v>
       </c>
       <c r="X54">
-        <v>0.9856488374403087</v>
+        <v>0.9856804824481136</v>
       </c>
       <c r="Y54">
         <v>0.9830591678619385</v>
@@ -5199,7 +5199,7 @@
         <v>56.743204455406456</v>
       </c>
       <c r="E55">
-        <v>58.18</v>
+        <v>57.36</v>
       </c>
       <c r="F55">
         <v>56.74</v>
@@ -5208,16 +5208,16 @@
         <v>111803.671671875</v>
       </c>
       <c r="H55">
-        <v>101661.64999999989</v>
+        <v>100718.25</v>
       </c>
       <c r="I55">
-        <v>96835.46000000015</v>
+        <v>97126.8999999999</v>
       </c>
       <c r="J55">
-        <v>-0.1338794285379467</v>
+        <v>-0.13127271629279716</v>
       </c>
       <c r="K55">
-        <v>-0.09071277821394126</v>
+        <v>-0.0991507837453572</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>0.7142086029052734</v>
       </c>
       <c r="X55">
-        <v>0.6614543163205797</v>
+        <v>0.6566702240503706</v>
       </c>
       <c r="Y55">
         <v>0.4353100657463074</v>
@@ -5303,16 +5303,16 @@
         <v>103219.02082812501</v>
       </c>
       <c r="H56">
-        <v>96140.8800000004</v>
+        <v>95509.22000000013</v>
       </c>
       <c r="I56">
-        <v>95933.09000000003</v>
+        <v>96042.63999999984</v>
       </c>
       <c r="J56">
-        <v>-0.07058709499150491</v>
+        <v>-0.06952575959885252</v>
       </c>
       <c r="K56">
-        <v>-0.06857399703404246</v>
+        <v>-0.0746936055609638</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>168.7324221607141</v>
       </c>
       <c r="E57">
-        <v>171.57</v>
+        <v>171.66</v>
       </c>
       <c r="F57">
         <v>168.73</v>
@@ -5383,16 +5383,16 @@
         <v>380573.5991171875</v>
       </c>
       <c r="H57">
-        <v>279210.8800000001</v>
+        <v>280203.1399999998</v>
       </c>
       <c r="I57">
-        <v>288784.7199999997</v>
+        <v>288563.15000000043</v>
       </c>
       <c r="J57">
-        <v>-0.24118561910261113</v>
+        <v>-0.24176781923555055</v>
       </c>
       <c r="K57">
-        <v>-0.26634196211276184</v>
+        <v>-0.26373468719326826</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>0.5803835690021515</v>
       </c>
       <c r="X57">
-        <v>0.6315674323779735</v>
+        <v>0.6315267567562867</v>
       </c>
       <c r="Y57">
         <v>0.4520184397697449</v>
@@ -5478,16 +5478,16 @@
         <v>376216.25653125</v>
       </c>
       <c r="H58">
-        <v>291866.9499999996</v>
+        <v>292049.4700000001</v>
       </c>
       <c r="I58">
-        <v>291818.6400000003</v>
+        <v>291761.80999999976</v>
       </c>
       <c r="J58">
-        <v>-0.22433272105092916</v>
+        <v>-0.22448377778761705</v>
       </c>
       <c r="K58">
-        <v>-0.22420431086354192</v>
+        <v>-0.22371916436380443</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>111.8848157134316</v>
       </c>
       <c r="E59">
-        <v>115.02</v>
+        <v>114.97</v>
       </c>
       <c r="F59">
         <v>111.85</v>
@@ -5558,16 +5558,16 @@
         <v>259544.44775</v>
       </c>
       <c r="H59">
-        <v>194989.27999999994</v>
+        <v>194907.94999999987</v>
       </c>
       <c r="I59">
-        <v>193298.7399999995</v>
+        <v>193358.7100000005</v>
       </c>
       <c r="J59">
-        <v>-0.2552383929777226</v>
+        <v>-0.25500733428808053</v>
       </c>
       <c r="K59">
-        <v>-0.24872490361335442</v>
+        <v>-0.24903826034552545</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>0.9448669254779816</v>
       </c>
       <c r="X59">
-        <v>0.9448813437381243</v>
+        <v>0.9448702388205317</v>
       </c>
       <c r="Y59">
         <v>0.8904971480369568</v>
@@ -5644,7 +5644,7 @@
         <v>109.86903584095278</v>
       </c>
       <c r="E60">
-        <v>110.58</v>
+        <v>110.54</v>
       </c>
       <c r="F60">
         <v>109.87</v>
@@ -5653,16 +5653,16 @@
         <v>272527.6270625</v>
       </c>
       <c r="H60">
-        <v>189821.53000000035</v>
+        <v>189193.36999999956</v>
       </c>
       <c r="I60">
-        <v>190048.94000000064</v>
+        <v>189924.7399999998</v>
       </c>
       <c r="J60">
-        <v>-0.30264339785112554</v>
+        <v>-0.30309913146367545</v>
       </c>
       <c r="K60">
-        <v>-0.30347784536182926</v>
+        <v>-0.3057827859903136</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>0.9668639302253723</v>
       </c>
       <c r="X60">
-        <v>0.9668767547494551</v>
+        <v>0.9668732639135708</v>
       </c>
       <c r="Y60">
         <v>0.9546698927879333</v>
@@ -5739,7 +5739,7 @@
         <v>451.4562124773123</v>
       </c>
       <c r="E61">
-        <v>451.33</v>
+        <v>451.37</v>
       </c>
       <c r="F61">
         <v>451.46</v>
@@ -5748,16 +5748,16 @@
         <v>910426.1154375001</v>
       </c>
       <c r="H61">
-        <v>782367.1599999971</v>
+        <v>778456.869999998</v>
       </c>
       <c r="I61">
-        <v>782867.660000003</v>
+        <v>781735.4600000015</v>
       </c>
       <c r="J61">
-        <v>-0.1401085198178873</v>
+        <v>-0.14135211331856076</v>
       </c>
       <c r="K61">
-        <v>-0.14065826239613627</v>
+        <v>-0.144953273197886</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5843,16 +5843,16 @@
         <v>1083195.76996875</v>
       </c>
       <c r="H62">
-        <v>883440.0500000028</v>
+        <v>880417.4399999998</v>
       </c>
       <c r="I62">
-        <v>884032.2200000017</v>
+        <v>878073.610000002</v>
       </c>
       <c r="J62">
-        <v>-0.18386662456639216</v>
+        <v>-0.18936757847075578</v>
       </c>
       <c r="K62">
-        <v>-0.1844133124472135</v>
+        <v>-0.18720376832213834</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5923,16 +5923,16 @@
         <v>1062625.4551796876</v>
       </c>
       <c r="H63">
-        <v>862444.2100000001</v>
+        <v>851145.6300000016</v>
       </c>
       <c r="I63">
-        <v>861089.1999999991</v>
+        <v>857294.1500000005</v>
       </c>
       <c r="J63">
-        <v>-0.18965878729642244</v>
+        <v>-0.19323017736759002</v>
       </c>
       <c r="K63">
-        <v>-0.18838363433128685</v>
+        <v>-0.19901633651710818</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -6003,16 +6003,16 @@
         <v>1044686.848125</v>
       </c>
       <c r="H64">
-        <v>802377.9799999996</v>
+        <v>804524.8799999984</v>
       </c>
       <c r="I64">
-        <v>803482.4600000002</v>
+        <v>804516.7299999979</v>
       </c>
       <c r="J64">
-        <v>-0.23088678541125748</v>
+        <v>-0.22989675667503476</v>
       </c>
       <c r="K64">
-        <v>-0.23194402088998767</v>
+        <v>-0.22988895529415673</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6083,16 +6083,16 @@
         <v>2267763.24325</v>
       </c>
       <c r="H65">
-        <v>1368111.3999999997</v>
+        <v>1365289.2900000021</v>
       </c>
       <c r="I65">
-        <v>1369518.230000005</v>
+        <v>1365390.45</v>
       </c>
       <c r="J65">
-        <v>-0.3960929413260499</v>
+        <v>-0.3979131401551346</v>
       </c>
       <c r="K65">
-        <v>-0.3967133014999758</v>
+        <v>-0.39795774798635286</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6163,16 +6163,16 @@
         <v>1913829.6795</v>
       </c>
       <c r="H66">
-        <v>1231509.7400000002</v>
+        <v>1230754.1199999969</v>
       </c>
       <c r="I66">
-        <v>1231365.3299999943</v>
+        <v>1232496.5000000007</v>
       </c>
       <c r="J66">
-        <v>-0.3565961782337412</v>
+        <v>-0.3560051277279815</v>
       </c>
       <c r="K66">
-        <v>-0.35652072219836206</v>
+        <v>-0.35691554312108953</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6243,16 +6243,16 @@
         <v>34614.4205</v>
       </c>
       <c r="H67">
-        <v>26637.46000000004</v>
+        <v>26684.019999999968</v>
       </c>
       <c r="I67">
-        <v>26712.810000000052</v>
+        <v>26640.179999999957</v>
       </c>
       <c r="J67">
-        <v>-0.22827510574674933</v>
+        <v>-0.2303733641879125</v>
       </c>
       <c r="K67">
-        <v>-0.23045194415431455</v>
+        <v>-0.22910684002351078</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
         <v>20633.5035</v>
       </c>
       <c r="H68">
-        <v>17196.809999999998</v>
+        <v>17186.86000000001</v>
       </c>
       <c r="I68">
-        <v>17190.36999999997</v>
+        <v>17232.639999999934</v>
       </c>
       <c r="J68">
-        <v>-0.16687100666157006</v>
+        <v>-0.16482239673936447</v>
       </c>
       <c r="K68">
-        <v>-0.16655889291898496</v>
+        <v>-0.16704111834424956</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6403,16 +6403,16 @@
         <v>1060573.5794375</v>
       </c>
       <c r="H69">
-        <v>849689.4400000012</v>
+        <v>848962.6199999995</v>
       </c>
       <c r="I69">
-        <v>849748.2200000014</v>
+        <v>849413.7800000021</v>
       </c>
       <c r="J69">
-        <v>-0.1987842838299959</v>
+        <v>-0.1990996226301352</v>
       </c>
       <c r="K69">
-        <v>-0.1988397066701833</v>
+        <v>-0.19952501508639633</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -6483,16 +6483,16 @@
         <v>129415.845</v>
       </c>
       <c r="H70">
-        <v>114440.9699999999</v>
+        <v>114531.87000000014</v>
       </c>
       <c r="I70">
-        <v>114410.4300000002</v>
+        <v>114381.82999999978</v>
       </c>
       <c r="J70">
-        <v>-0.11594727832592527</v>
+        <v>-0.11616827135811861</v>
       </c>
       <c r="K70">
-        <v>-0.11571129485728816</v>
+        <v>-0.11500890791231831</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -6563,16 +6563,16 @@
         <v>66440.65612500001</v>
       </c>
       <c r="H71">
-        <v>55365.099999999955</v>
+        <v>55380.380000000114</v>
       </c>
       <c r="I71">
-        <v>55411.01000000004</v>
+        <v>55433.85999999997</v>
       </c>
       <c r="J71">
-        <v>-0.16600748349397745</v>
+        <v>-0.16566356756459613</v>
       </c>
       <c r="K71">
-        <v>-0.16669847606806806</v>
+        <v>-0.16646849640062752</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6866,13 +6866,13 @@
         <v>6850.44</v>
       </c>
       <c r="D2">
-        <v>11750669.109999998</v>
+        <v>11748293.760000022</v>
       </c>
       <c r="E2">
         <v>6850.44</v>
       </c>
       <c r="F2">
-        <v>11749716.379999992</v>
+        <v>11746907.960000018</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -6906,13 +6906,13 @@
         <v>1693.19</v>
       </c>
       <c r="D3">
-        <v>2936828.719999997</v>
+        <v>2937445.209999999</v>
       </c>
       <c r="E3">
         <v>1693.19</v>
       </c>
       <c r="F3">
-        <v>2937236.7100000083</v>
+        <v>2937699.7800000003</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6946,13 +6946,13 @@
         <v>2906.82</v>
       </c>
       <c r="D4">
-        <v>5046186.889999997</v>
+        <v>5045869.819999991</v>
       </c>
       <c r="E4">
         <v>2906.82</v>
       </c>
       <c r="F4">
-        <v>5045631.119999985</v>
+        <v>5045545.209999988</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -6986,13 +6986,13 @@
         <v>3104.91</v>
       </c>
       <c r="D5">
-        <v>5357884.150000015</v>
+        <v>5357584.599999997</v>
       </c>
       <c r="E5">
         <v>3104.91</v>
       </c>
       <c r="F5">
-        <v>5357553.279999997</v>
+        <v>5358992.709999977</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7026,13 +7026,13 @@
         <v>930.44</v>
       </c>
       <c r="D6">
-        <v>1590331.260000006</v>
+        <v>1586904.020000001</v>
       </c>
       <c r="E6">
         <v>930.44</v>
       </c>
       <c r="F6">
-        <v>1589563.1200000024</v>
+        <v>1586967.599999998</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7063,16 +7063,16 @@
         </is>
       </c>
       <c r="C7">
-        <v>872.5</v>
+        <v>872.62</v>
       </c>
       <c r="D7">
-        <v>1474814.5499999996</v>
+        <v>1470648.6999999953</v>
       </c>
       <c r="E7">
         <v>866.55</v>
       </c>
       <c r="F7">
-        <v>1479402.0700000008</v>
+        <v>1475226.4500000032</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>0.6519851982593536</v>
       </c>
       <c r="O7">
-        <v>0.6512579033929947</v>
+        <v>0.6512806921393035</v>
       </c>
       <c r="P7">
         <v>0.5486889481544495</v>
@@ -7118,16 +7118,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>875.18</v>
+        <v>875.52</v>
       </c>
       <c r="D8">
-        <v>1427502.510000007</v>
+        <v>1419928.7399999967</v>
       </c>
       <c r="E8">
         <v>872.61</v>
       </c>
       <c r="F8">
-        <v>1431292.3500000006</v>
+        <v>1431116.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>0.6965939402580261</v>
       </c>
       <c r="O8">
-        <v>0.6964081099397869</v>
+        <v>0.6963873350360231</v>
       </c>
       <c r="P8">
         <v>0.6317542791366577</v>
@@ -7176,13 +7176,13 @@
         <v>2943.28</v>
       </c>
       <c r="D9">
-        <v>5109330.949999997</v>
+        <v>5110004.719999988</v>
       </c>
       <c r="E9">
         <v>2943.28</v>
       </c>
       <c r="F9">
-        <v>5109272.099999999</v>
+        <v>5107081.200000004</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7216,13 +7216,13 @@
         <v>970.93</v>
       </c>
       <c r="D10">
-        <v>1190379.199999998</v>
+        <v>1160505.19</v>
       </c>
       <c r="E10">
         <v>970.93</v>
       </c>
       <c r="F10">
-        <v>1186057.9000000013</v>
+        <v>1161096.8499999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7256,13 +7256,13 @@
         <v>272.61</v>
       </c>
       <c r="D11">
-        <v>472462.0000000018</v>
+        <v>472039.910000001</v>
       </c>
       <c r="E11">
         <v>272.61</v>
       </c>
       <c r="F11">
-        <v>472107.95000000065</v>
+        <v>472819.9899999998</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -7293,16 +7293,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>114.65</v>
+        <v>115.89</v>
       </c>
       <c r="D12">
-        <v>202495.6600000001</v>
+        <v>195755.7500000005</v>
       </c>
       <c r="E12">
         <v>110.34</v>
       </c>
       <c r="F12">
-        <v>176056.72999999992</v>
+        <v>172393.4300000006</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>0.6553257405757904</v>
       </c>
       <c r="O12">
-        <v>0.6530525516122397</v>
+        <v>0.6541229435415905</v>
       </c>
       <c r="P12">
         <v>0.5647161602973938</v>
@@ -7348,16 +7348,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>220.77</v>
+        <v>218.9</v>
       </c>
       <c r="D13">
-        <v>358195.0000000003</v>
+        <v>391518.54999999935</v>
       </c>
       <c r="E13">
         <v>214.57</v>
       </c>
       <c r="F13">
-        <v>368960.7099999988</v>
+        <v>370310.4100000006</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>0.8098851243654887</v>
       </c>
       <c r="O13">
-        <v>0.7402637658592744</v>
+        <v>0.7389471297125113</v>
       </c>
       <c r="P13">
         <v>0.5294176340103149</v>
@@ -7406,13 +7406,13 @@
         <v>2610.32</v>
       </c>
       <c r="D14">
-        <v>4398730.870000009</v>
+        <v>4401692.920000008</v>
       </c>
       <c r="E14">
         <v>2610.32</v>
       </c>
       <c r="F14">
-        <v>4400881.609999997</v>
+        <v>4401265.419999995</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         <v>4092.56</v>
       </c>
       <c r="D15">
-        <v>4612887.960000006</v>
+        <v>4655078.979999998</v>
       </c>
       <c r="E15">
         <v>4092.56</v>
       </c>
       <c r="F15">
-        <v>4623988.199999998</v>
+        <v>4660354.21</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7486,13 +7486,13 @@
         <v>275.65</v>
       </c>
       <c r="D16">
-        <v>454454.1599999994</v>
+        <v>453443.55000000016</v>
       </c>
       <c r="E16">
         <v>275.65</v>
       </c>
       <c r="F16">
-        <v>453997.5499999992</v>
+        <v>453614.39000000025</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7526,13 +7526,13 @@
         <v>1505.95</v>
       </c>
       <c r="D17">
-        <v>2609095.2300000046</v>
+        <v>2608870.07</v>
       </c>
       <c r="E17">
         <v>1505.95</v>
       </c>
       <c r="F17">
-        <v>2608828.890000008</v>
+        <v>2609248.409999997</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7563,16 +7563,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>170.25</v>
+        <v>170.33</v>
       </c>
       <c r="D18">
-        <v>282227.7499999999</v>
+        <v>283652.3799999994</v>
       </c>
       <c r="E18">
         <v>167.51</v>
       </c>
       <c r="F18">
-        <v>279951.4500000005</v>
+        <v>280137.0900000003</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>0.9814960360527039</v>
       </c>
       <c r="O18">
-        <v>0.9815501190966867</v>
+        <v>0.9815527296914881</v>
       </c>
       <c r="P18">
         <v>0.9661091566085815</v>
@@ -7618,16 +7618,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>807.71</v>
+        <v>806.14</v>
       </c>
       <c r="D19">
-        <v>1309712.8800000087</v>
+        <v>1335372.8400000012</v>
       </c>
       <c r="E19">
         <v>793.68</v>
       </c>
       <c r="F19">
-        <v>1221695.8700000027</v>
+        <v>1251665.8999999983</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>0.5739879906177521</v>
       </c>
       <c r="O19">
-        <v>0.573995562871005</v>
+        <v>0.5740174029920202</v>
       </c>
       <c r="P19">
         <v>0.5584376454353333</v>
@@ -7673,16 +7673,16 @@
         </is>
       </c>
       <c r="C20">
-        <v>470.62</v>
+        <v>469.33</v>
       </c>
       <c r="D20">
-        <v>734897.1999999968</v>
+        <v>781931.3800000009</v>
       </c>
       <c r="E20">
         <v>459.9</v>
       </c>
       <c r="F20">
-        <v>750244.2199999979</v>
+        <v>753835.8299999996</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>0.5485995511213938</v>
       </c>
       <c r="O20">
-        <v>0.573283185298977</v>
+        <v>0.5737625769305833</v>
       </c>
       <c r="P20">
         <v>0.49337705969810486</v>
@@ -7731,13 +7731,13 @@
         <v>738.25</v>
       </c>
       <c r="D21">
-        <v>877633.200000001</v>
+        <v>779971.2699999986</v>
       </c>
       <c r="E21">
         <v>738.25</v>
       </c>
       <c r="F21">
-        <v>901705.450000002</v>
+        <v>785411.4999999987</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -7768,16 +7768,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>476.35</v>
+        <v>476.25</v>
       </c>
       <c r="D22">
-        <v>750668.7899999996</v>
+        <v>714505.2299999994</v>
       </c>
       <c r="E22">
         <v>476.33</v>
       </c>
       <c r="F22">
-        <v>752372.6999999979</v>
+        <v>703873.2100000003</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>0.4284673035144806</v>
       </c>
       <c r="O22">
-        <v>0.4284673035144806</v>
+        <v>0.42846730351448065</v>
       </c>
       <c r="P22">
         <v>0.4284673035144806</v>
@@ -7823,16 +7823,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>475.21</v>
+        <v>475.37</v>
       </c>
       <c r="D23">
-        <v>801171.3399999978</v>
+        <v>816880.2600000006</v>
       </c>
       <c r="E23">
         <v>467.82</v>
       </c>
       <c r="F23">
-        <v>808915.1500000001</v>
+        <v>808832.0199999993</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>0.6775287389755249</v>
       </c>
       <c r="O23">
-        <v>0.6276030359295445</v>
+        <v>0.6266021872298921</v>
       </c>
       <c r="P23">
         <v>0.46839380264282227</v>
@@ -7881,13 +7881,13 @@
         <v>759.24</v>
       </c>
       <c r="D24">
-        <v>1317595.4699999967</v>
+        <v>1317286.159999994</v>
       </c>
       <c r="E24">
         <v>759.24</v>
       </c>
       <c r="F24">
-        <v>1316914.5099999984</v>
+        <v>1317638.6099999982</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -7921,13 +7921,13 @@
         <v>2398.34</v>
       </c>
       <c r="D25">
-        <v>4161942.5100000016</v>
+        <v>4163072.9299999895</v>
       </c>
       <c r="E25">
         <v>2398.34</v>
       </c>
       <c r="F25">
-        <v>4162731.5000000102</v>
+        <v>4163707.969999989</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7961,13 +7961,13 @@
         <v>2320.8</v>
       </c>
       <c r="D26">
-        <v>3507124.8299999936</v>
+        <v>3503571.78999999</v>
       </c>
       <c r="E26">
         <v>2320.8</v>
       </c>
       <c r="F26">
-        <v>3514969.899999995</v>
+        <v>3504827.670000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -8001,13 +8001,13 @@
         <v>1297.8</v>
       </c>
       <c r="D27">
-        <v>2204445.7400000067</v>
+        <v>2204369.89</v>
       </c>
       <c r="E27">
         <v>1297.8</v>
       </c>
       <c r="F27">
-        <v>2204028.2899999986</v>
+        <v>2203776.8700000006</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8041,13 +8041,13 @@
         <v>238.47</v>
       </c>
       <c r="D28">
-        <v>402066.18999999965</v>
+        <v>402128.86999999906</v>
       </c>
       <c r="E28">
         <v>238.47</v>
       </c>
       <c r="F28">
-        <v>402468.99000000005</v>
+        <v>402039.59999999905</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8081,13 +8081,13 @@
         <v>799.84</v>
       </c>
       <c r="D29">
-        <v>1379738.2499999984</v>
+        <v>1378617.7299999993</v>
       </c>
       <c r="E29">
         <v>799.84</v>
       </c>
       <c r="F29">
-        <v>1378389.9100000053</v>
+        <v>1378742.9999999932</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8121,13 +8121,13 @@
         <v>575.41</v>
       </c>
       <c r="D30">
-        <v>973503.4599999986</v>
+        <v>972390.6400000018</v>
       </c>
       <c r="E30">
         <v>575.41</v>
       </c>
       <c r="F30">
-        <v>973429.3599999979</v>
+        <v>973099.9899999995</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -8161,13 +8161,13 @@
         <v>301.74</v>
       </c>
       <c r="D31">
-        <v>489840.9200000032</v>
+        <v>488296.4300000003</v>
       </c>
       <c r="E31">
         <v>301.74</v>
       </c>
       <c r="F31">
-        <v>487262.08000000083</v>
+        <v>488103.34000000014</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -8201,13 +8201,13 @@
         <v>451.42</v>
       </c>
       <c r="D32">
-        <v>764302.9500000017</v>
+        <v>763551.4800000003</v>
       </c>
       <c r="E32">
         <v>451.42</v>
       </c>
       <c r="F32">
-        <v>764168.6800000012</v>
+        <v>763171.9400000019</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -8241,13 +8241,13 @@
         <v>1432.54</v>
       </c>
       <c r="D33">
-        <v>2381664.61</v>
+        <v>2379893.2999999984</v>
       </c>
       <c r="E33">
         <v>1432.54</v>
       </c>
       <c r="F33">
-        <v>2383809.0100000016</v>
+        <v>2379380.0700000026</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
